--- a/model/ABNB_official_model_complete.xlsx
+++ b/model/ABNB_official_model_complete.xlsx
@@ -20,12 +20,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="0.000000"/>
     <numFmt numFmtId="168" formatCode="0.0000"/>
+    <numFmt numFmtId="169" formatCode="0.000%"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -117,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -153,7 +154,11 @@
     <xf numFmtId="164" fontId="7" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1479,7 +1484,7 @@
       </s:c>
       <s:c r="B7" s="3" t="inlineStr">
         <s:is>
-          <s:t>Nights: built (DEC-0029 base 146.8m). ADR: built (ADR_Engine; pre-registered FX identity promoted, ex-FX mechanism with the bundle lapping on filed dates; proposed DEC-0034/0035 pending Theo), then extended with the v2 geo-mix layer and hardened by the four mitigations of 22 Sep (block G; DEC-0037–0041 pending Theo). Base ADR path unchanged by the mitigations: 3Q26 $177.68, 4Q26 $173.03. GBV = nights × ADR on Income_Statement row 8. Next: take rate / revenue, together, one at a time.</s:t>
+          <s:t>Nights: built (DEC-0029 base 146.8m). ADR: built (ADR_Engine; pre-registered FX identity promoted, ex-FX mechanism with the bundle lapping on filed dates; proposed DEC-0034/0035 pending Theo), then extended with the v2 geo-mix layer and hardened by the four mitigations of 22 Sep (block G; DEC-0037–0041 pending Theo). Base ADR path unchanged by the mitigations: 3Q26 $177.68, 4Q26 $173.03. GBV = nights × ADR on Income_Statement row 8. Income statement: history 1Q23-2Q26 plugged from the reconciled financial panel; forecast cost lines, SBC, D&amp;A and below-the-line plugged from the 40_line_build base (DEC-0022); take rate Street-implied for 3Q26-4Q26 (DEC-0018) and seasonal naive thereafter, so the margin is an output of our own nights x ADR. Open: DEC-0023 hosting step.</s:t>
         </s:is>
       </s:c>
     </s:row>
@@ -12757,7 +12762,7 @@
     <s:outlinePr summaryBelow="1" summaryRight="1"/>
     <s:pageSetUpPr/>
   </s:sheetPr>
-  <s:dimension ref="A1:AC36"/>
+  <s:dimension ref="A1:AC45"/>
   <s:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <s:cols>
     <s:col width="52" customWidth="1" min="1" max="1"/>
@@ -13192,7 +13197,11 @@
           <s:t>Lines to build together (in order) — empty until each has its rationale file</s:t>
         </s:is>
       </s:c>
-      <s:c r="B7" s="5" t="n"/>
+      <s:c r="B7" s="6" t="inlineStr">
+        <s:is>
+          <s:t>history 1Q23-2Q26 plugged from 02_panel_quarterly.csv (reported); forecast cost lines and below-the-line plugged from 40_line_build base (DEC-0022); blue = plug, black = formula</s:t>
+        </s:is>
+      </s:c>
       <s:c r="C7" s="5" t="n"/>
       <s:c r="D7" s="5" t="n"/>
       <s:c r="E7" s="5" t="n"/>
@@ -13569,12 +13578,97 @@
           <s:t>Revenue</s:t>
         </s:is>
       </s:c>
-      <s:c r="Q12" s="31" t="n"/>
-      <s:c r="R12" s="31" t="n"/>
-      <s:c r="S12" s="31" t="n"/>
-      <s:c r="T12" s="31" t="n"/>
-      <s:c r="U12" s="31" t="n"/>
-      <s:c r="V12" s="31" t="n"/>
+      <s:c r="B12" s="4" t="inlineStr">
+        <s:is>
+          <s:t>A: reported. E: = GBV x take rate (DEC-0018), so revenue is an output of lines 1-2</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C12" s="31" t="n">
+        <s:v>1818</s:v>
+      </s:c>
+      <s:c r="D12" s="31" t="n">
+        <s:v>2484</s:v>
+      </s:c>
+      <s:c r="E12" s="31" t="n">
+        <s:v>3397</s:v>
+      </s:c>
+      <s:c r="F12" s="31" t="n">
+        <s:v>2218</s:v>
+      </s:c>
+      <s:c r="G12" s="31" t="n">
+        <s:v>2142</s:v>
+      </s:c>
+      <s:c r="H12" s="31" t="n">
+        <s:v>2748</s:v>
+      </s:c>
+      <s:c r="I12" s="31" t="n">
+        <s:v>3732</s:v>
+      </s:c>
+      <s:c r="J12" s="31" t="n">
+        <s:v>2480</s:v>
+      </s:c>
+      <s:c r="K12" s="31" t="n">
+        <s:v>2272</s:v>
+      </s:c>
+      <s:c r="L12" s="31" t="n">
+        <s:v>3096</s:v>
+      </s:c>
+      <s:c r="M12" s="31" t="n">
+        <s:v>4095</s:v>
+      </s:c>
+      <s:c r="N12" s="31" t="n">
+        <s:v>2778</s:v>
+      </s:c>
+      <s:c r="O12" s="31" t="n">
+        <s:v>2678</s:v>
+      </s:c>
+      <s:c r="P12" s="31" t="n">
+        <s:v>3608</s:v>
+      </s:c>
+      <s:c r="Q12" s="32">
+        <s:f>Q8*1000*Q14</s:f>
+        <s:v>4690.915404262231</s:v>
+      </s:c>
+      <s:c r="R12" s="32">
+        <s:f>R8*1000*R14</s:f>
+        <s:v>3140.7997203637324</s:v>
+      </s:c>
+      <s:c r="S12" s="32">
+        <s:f>S8*1000*S14</s:f>
+        <s:v>2955.1010577201146</s:v>
+      </s:c>
+      <s:c r="T12" s="32">
+        <s:f>T8*1000*T14</s:f>
+        <s:v>3925.6265585425626</s:v>
+      </s:c>
+      <s:c r="U12" s="32">
+        <s:f>U8*1000*U14</s:f>
+        <s:v>5117.767615964276</s:v>
+      </s:c>
+      <s:c r="V12" s="32">
+        <s:f>V8*1000*V14</s:f>
+        <s:v>3426.2315257790865</s:v>
+      </s:c>
+      <s:c r="X12" s="32">
+        <s:f>SUM(C12:F12)</s:f>
+        <s:v>9917.0</s:v>
+      </s:c>
+      <s:c r="Y12" s="32">
+        <s:f>SUM(G12:J12)</s:f>
+        <s:v>11102.0</s:v>
+      </s:c>
+      <s:c r="Z12" s="32">
+        <s:f>SUM(K12:N12)</s:f>
+        <s:v>12241.0</s:v>
+      </s:c>
+      <s:c r="AA12" s="32">
+        <s:f>SUM(O12:R12)</s:f>
+        <s:v>14117.715124625964</s:v>
+      </s:c>
+      <s:c r="AB12" s="32">
+        <s:f>SUM(S12:V12)</s:f>
+        <s:v>15424.72675800604</s:v>
+      </s:c>
     </s:row>
     <s:row r="13">
       <s:c r="A13" s="8" t="inlineStr">
@@ -13582,12 +13676,86 @@
           <s:t xml:space="preserve">    y/y</s:t>
         </s:is>
       </s:c>
-      <s:c r="Q13" s="31" t="n"/>
-      <s:c r="R13" s="31" t="n"/>
-      <s:c r="S13" s="31" t="n"/>
-      <s:c r="T13" s="31" t="n"/>
-      <s:c r="U13" s="31" t="n"/>
-      <s:c r="V13" s="31" t="n"/>
+      <s:c r="G13" s="33">
+        <s:f>G12/C12-1</s:f>
+        <s:v>0.17821782178217815</s:v>
+      </s:c>
+      <s:c r="H13" s="33">
+        <s:f>H12/D12-1</s:f>
+        <s:v>0.106280193236715</s:v>
+      </s:c>
+      <s:c r="I13" s="33">
+        <s:f>I12/E12-1</s:f>
+        <s:v>0.09861642625846345</s:v>
+      </s:c>
+      <s:c r="J13" s="33">
+        <s:f>J12/F12-1</s:f>
+        <s:v>0.11812443642921555</s:v>
+      </s:c>
+      <s:c r="K13" s="33">
+        <s:f>K12/G12-1</s:f>
+        <s:v>0.06069094304388423</s:v>
+      </s:c>
+      <s:c r="L13" s="33">
+        <s:f>L12/H12-1</s:f>
+        <s:v>0.1266375545851528</s:v>
+      </s:c>
+      <s:c r="M13" s="33">
+        <s:f>M12/I12-1</s:f>
+        <s:v>0.09726688102893899</s:v>
+      </s:c>
+      <s:c r="N13" s="33">
+        <s:f>N12/J12-1</s:f>
+        <s:v>0.1201612903225806</s:v>
+      </s:c>
+      <s:c r="O13" s="33">
+        <s:f>O12/K12-1</s:f>
+        <s:v>0.1786971830985915</s:v>
+      </s:c>
+      <s:c r="P13" s="33">
+        <s:f>P12/L12-1</s:f>
+        <s:v>0.1653746770025839</s:v>
+      </s:c>
+      <s:c r="Q13" s="33">
+        <s:f>Q12/M12-1</s:f>
+        <s:v>0.14552268724352402</s:v>
+      </s:c>
+      <s:c r="R13" s="33">
+        <s:f>R12/N12-1</s:f>
+        <s:v>0.13059745153482094</s:v>
+      </s:c>
+      <s:c r="S13" s="33">
+        <s:f>S12/O12-1</s:f>
+        <s:v>0.10347313581781714</s:v>
+      </s:c>
+      <s:c r="T13" s="33">
+        <s:f>T12/P12-1</s:f>
+        <s:v>0.08803396855392531</s:v>
+      </s:c>
+      <s:c r="U13" s="33">
+        <s:f>U12/Q12-1</s:f>
+        <s:v>0.09099550405752388</s:v>
+      </s:c>
+      <s:c r="V13" s="33">
+        <s:f>V12/R12-1</s:f>
+        <s:v>0.09087870314198154</s:v>
+      </s:c>
+      <s:c r="Y13" s="33">
+        <s:f>Y12/X12-1</s:f>
+        <s:v>0.11949178178884745</s:v>
+      </s:c>
+      <s:c r="Z13" s="33">
+        <s:f>Z12/Y12-1</s:f>
+        <s:v>0.10259412718429117</s:v>
+      </s:c>
+      <s:c r="AA13" s="33">
+        <s:f>AA12/Z12-1</s:f>
+        <s:v>0.1533138734274948</s:v>
+      </s:c>
+      <s:c r="AB13" s="33">
+        <s:f>AB12/AA12-1</s:f>
+        <s:v>0.09257954434143634</s:v>
+      </s:c>
     </s:row>
     <s:row r="14">
       <s:c r="A14" s="8" t="inlineStr">
@@ -13595,12 +13763,105 @@
           <s:t xml:space="preserve">    Take rate (revenue / GBV)</s:t>
         </s:is>
       </s:c>
-      <s:c r="Q14" s="31" t="n"/>
-      <s:c r="R14" s="31" t="n"/>
-      <s:c r="S14" s="31" t="n"/>
-      <s:c r="T14" s="31" t="n"/>
-      <s:c r="U14" s="31" t="n"/>
-      <s:c r="V14" s="31" t="n"/>
+      <s:c r="B14" s="4" t="inlineStr">
+        <s:is>
+          <s:t>A: = revenue / GBV. E: 3Q26-4Q26 Street-implied; 1Q27+ seasonal naive tau[q-4], no drift</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C14" s="34">
+        <s:f>C12/(C8*1000)</s:f>
+        <s:v>0.08913130949043023</s:v>
+      </s:c>
+      <s:c r="D14" s="34">
+        <s:f>D12/(D8*1000)</s:f>
+        <s:v>0.12999960068560662</s:v>
+      </s:c>
+      <s:c r="E14" s="34">
+        <s:f>E12/(E8*1000)</s:f>
+        <s:v>0.1859513813499906</s:v>
+      </s:c>
+      <s:c r="F14" s="34">
+        <s:f>F12/(F8*1000)</s:f>
+        <s:v>0.14323609208543744</s:v>
+      </s:c>
+      <s:c r="G14" s="34">
+        <s:f>G12/(G8*1000)</s:f>
+        <s:v>0.09343964688712492</s:v>
+      </s:c>
+      <s:c r="H14" s="34">
+        <s:f>H12/(H8*1000)</s:f>
+        <s:v>0.12957250550647786</s:v>
+      </s:c>
+      <s:c r="I14" s="34">
+        <s:f>I12/(I8*1000)</s:f>
+        <s:v>0.18571791419474068</s:v>
+      </s:c>
+      <s:c r="J14" s="34">
+        <s:f>J12/(J8*1000)</s:f>
+        <s:v>0.1412909779443644</s:v>
+      </s:c>
+      <s:c r="K14" s="34">
+        <s:f>K12/(K8*1000)</s:f>
+        <s:v>0.0926637626039235</s:v>
+      </s:c>
+      <s:c r="L14" s="34">
+        <s:f>L12/(L8*1000)</s:f>
+        <s:v>0.13202495578699155</s:v>
+      </s:c>
+      <s:c r="M14" s="34">
+        <s:f>M12/(M8*1000)</s:f>
+        <s:v>0.17894329852758725</s:v>
+      </s:c>
+      <s:c r="N14" s="34">
+        <s:f>N12/(N8*1000)</s:f>
+        <s:v>0.13604663275034232</s:v>
+      </s:c>
+      <s:c r="O14" s="34">
+        <s:f>O12/(O8*1000)</s:f>
+        <s:v>0.09177115030305041</s:v>
+      </s:c>
+      <s:c r="P14" s="34">
+        <s:f>P12/(P8*1000)</s:f>
+        <s:v>0.13241747515768526</s:v>
+      </s:c>
+      <s:c r="Q14" s="35" t="n">
+        <s:v>0.1798321124223617</s:v>
+      </s:c>
+      <s:c r="R14" s="35" t="n">
+        <s:v>0.137720607259622</s:v>
+      </s:c>
+      <s:c r="S14" s="35" t="n">
+        <s:v>0.09171</s:v>
+      </s:c>
+      <s:c r="T14" s="35" t="n">
+        <s:v>0.13265</s:v>
+      </s:c>
+      <s:c r="U14" s="35" t="n">
+        <s:v>0.1798321124223617</s:v>
+      </s:c>
+      <s:c r="V14" s="35" t="n">
+        <s:v>0.137720607259622</s:v>
+      </s:c>
+      <s:c r="X14" s="34">
+        <s:f>X12/(SUM(C8:F8)*1000)</s:f>
+        <s:v>0.13537131709343467</s:v>
+      </s:c>
+      <s:c r="Y14" s="34">
+        <s:f>Y12/(SUM(G8:J8)*1000)</s:f>
+        <s:v>0.13575527161674344</s:v>
+      </s:c>
+      <s:c r="Z14" s="34">
+        <s:f>Z12/(SUM(K8:N8)*1000)</s:f>
+        <s:v>0.13411461276380415</s:v>
+      </s:c>
+      <s:c r="AA14" s="34">
+        <s:f>AA12/(SUM(O8:R8)*1000)</s:f>
+        <s:v>0.1340471766436925</s:v>
+      </s:c>
+      <s:c r="AB14" s="34">
+        <s:f>AB12/(SUM(S8:V8)*1000)</s:f>
+        <s:v>0.13395005663999168</s:v>
+      </s:c>
     </s:row>
     <s:row r="16">
       <s:c r="A16" s="8" t="inlineStr">
@@ -13608,12 +13869,91 @@
           <s:t xml:space="preserve">    Cost of revenue (cash)</s:t>
         </s:is>
       </s:c>
-      <s:c r="Q16" s="31" t="n"/>
-      <s:c r="R16" s="31" t="n"/>
-      <s:c r="S16" s="31" t="n"/>
-      <s:c r="T16" s="31" t="n"/>
-      <s:c r="U16" s="31" t="n"/>
-      <s:c r="V16" s="31" t="n"/>
+      <s:c r="B16" s="4" t="inlineStr">
+        <s:is>
+          <s:t>cash = GAAP less SBC. A: 02_panel_quarterly. E: 40_line_build base, carried in dollars (DEC-0022)</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C16" s="31" t="n">
+        <s:v>428</s:v>
+      </s:c>
+      <s:c r="D16" s="31" t="n">
+        <s:v>432</s:v>
+      </s:c>
+      <s:c r="E16" s="31" t="n">
+        <s:v>459</s:v>
+      </s:c>
+      <s:c r="F16" s="31" t="n">
+        <s:v>384</s:v>
+      </s:c>
+      <s:c r="G16" s="31" t="n">
+        <s:v>480</s:v>
+      </s:c>
+      <s:c r="H16" s="31" t="n">
+        <s:v>506</s:v>
+      </s:c>
+      <s:c r="I16" s="31" t="n">
+        <s:v>465</s:v>
+      </s:c>
+      <s:c r="J16" s="31" t="n">
+        <s:v>427</s:v>
+      </s:c>
+      <s:c r="K16" s="31" t="n">
+        <s:v>506</s:v>
+      </s:c>
+      <s:c r="L16" s="31" t="n">
+        <s:v>544</s:v>
+      </s:c>
+      <s:c r="M16" s="31" t="n">
+        <s:v>549</s:v>
+      </s:c>
+      <s:c r="N16" s="31" t="n">
+        <s:v>487</s:v>
+      </s:c>
+      <s:c r="O16" s="31" t="n">
+        <s:v>581</s:v>
+      </s:c>
+      <s:c r="P16" s="31" t="n">
+        <s:v>633</s:v>
+      </s:c>
+      <s:c r="Q16" s="31" t="n">
+        <s:v>640.7841188023608</s:v>
+      </s:c>
+      <s:c r="R16" s="31" t="n">
+        <s:v>578.0394574666427</s:v>
+      </s:c>
+      <s:c r="S16" s="31" t="n">
+        <s:v>706.0035882028698</s:v>
+      </s:c>
+      <s:c r="T16" s="31" t="n">
+        <s:v>727.2995429788907</s:v>
+      </s:c>
+      <s:c r="U16" s="31" t="n">
+        <s:v>699.4536785339944</s:v>
+      </s:c>
+      <s:c r="V16" s="31" t="n">
+        <s:v>626.8522820155006</s:v>
+      </s:c>
+      <s:c r="X16" s="32">
+        <s:f>SUM(C16:F16)</s:f>
+        <s:v>1703.0</s:v>
+      </s:c>
+      <s:c r="Y16" s="32">
+        <s:f>SUM(G16:J16)</s:f>
+        <s:v>1878.0</s:v>
+      </s:c>
+      <s:c r="Z16" s="32">
+        <s:f>SUM(K16:N16)</s:f>
+        <s:v>2086.0</s:v>
+      </s:c>
+      <s:c r="AA16" s="32">
+        <s:f>SUM(O16:R16)</s:f>
+        <s:v>2432.8235762690038</s:v>
+      </s:c>
+      <s:c r="AB16" s="32">
+        <s:f>SUM(S16:V16)</s:f>
+        <s:v>2759.609091731255</s:v>
+      </s:c>
     </s:row>
     <s:row r="17">
       <s:c r="A17" s="8" t="inlineStr">
@@ -13621,12 +13961,86 @@
           <s:t xml:space="preserve">    Operations &amp; support (cash)</s:t>
         </s:is>
       </s:c>
-      <s:c r="Q17" s="31" t="n"/>
-      <s:c r="R17" s="31" t="n"/>
-      <s:c r="S17" s="31" t="n"/>
-      <s:c r="T17" s="31" t="n"/>
-      <s:c r="U17" s="31" t="n"/>
-      <s:c r="V17" s="31" t="n"/>
+      <s:c r="C17" s="31" t="n">
+        <s:v>267</s:v>
+      </s:c>
+      <s:c r="D17" s="31" t="n">
+        <s:v>298</s:v>
+      </s:c>
+      <s:c r="E17" s="31" t="n">
+        <s:v>299</s:v>
+      </s:c>
+      <s:c r="F17" s="31" t="n">
+        <s:v>254</s:v>
+      </s:c>
+      <s:c r="G17" s="31" t="n">
+        <s:v>266</s:v>
+      </s:c>
+      <s:c r="H17" s="31" t="n">
+        <s:v>314</s:v>
+      </s:c>
+      <s:c r="I17" s="31" t="n">
+        <s:v>347</s:v>
+      </s:c>
+      <s:c r="J17" s="31" t="n">
+        <s:v>265</s:v>
+      </s:c>
+      <s:c r="K17" s="31" t="n">
+        <s:v>282</s:v>
+      </s:c>
+      <s:c r="L17" s="31" t="n">
+        <s:v>309</s:v>
+      </s:c>
+      <s:c r="M17" s="31" t="n">
+        <s:v>343</s:v>
+      </s:c>
+      <s:c r="N17" s="31" t="n">
+        <s:v>303</s:v>
+      </s:c>
+      <s:c r="O17" s="31" t="n">
+        <s:v>301</s:v>
+      </s:c>
+      <s:c r="P17" s="31" t="n">
+        <s:v>323</s:v>
+      </s:c>
+      <s:c r="Q17" s="31" t="n">
+        <s:v>361.4430867108318</s:v>
+      </s:c>
+      <s:c r="R17" s="31" t="n">
+        <s:v>318.2870944871431</s:v>
+      </s:c>
+      <s:c r="S17" s="31" t="n">
+        <s:v>319.0860911068342</s:v>
+      </s:c>
+      <s:c r="T17" s="31" t="n">
+        <s:v>340.9682435981541</s:v>
+      </s:c>
+      <s:c r="U17" s="31" t="n">
+        <s:v>381.7590955367162</s:v>
+      </s:c>
+      <s:c r="V17" s="31" t="n">
+        <s:v>336.0624813662569</s:v>
+      </s:c>
+      <s:c r="X17" s="32">
+        <s:f>SUM(C17:F17)</s:f>
+        <s:v>1118.0</s:v>
+      </s:c>
+      <s:c r="Y17" s="32">
+        <s:f>SUM(G17:J17)</s:f>
+        <s:v>1192.0</s:v>
+      </s:c>
+      <s:c r="Z17" s="32">
+        <s:f>SUM(K17:N17)</s:f>
+        <s:v>1237.0</s:v>
+      </s:c>
+      <s:c r="AA17" s="32">
+        <s:f>SUM(O17:R17)</s:f>
+        <s:v>1303.7301811979748</s:v>
+      </s:c>
+      <s:c r="AB17" s="32">
+        <s:f>SUM(S17:V17)</s:f>
+        <s:v>1377.8759116079614</s:v>
+      </s:c>
     </s:row>
     <s:row r="18">
       <s:c r="A18" s="8" t="inlineStr">
@@ -13634,12 +14048,86 @@
           <s:t xml:space="preserve">    Product development (cash)</s:t>
         </s:is>
       </s:c>
-      <s:c r="Q18" s="31" t="n"/>
-      <s:c r="R18" s="31" t="n"/>
-      <s:c r="S18" s="31" t="n"/>
-      <s:c r="T18" s="31" t="n"/>
-      <s:c r="U18" s="31" t="n"/>
-      <s:c r="V18" s="31" t="n"/>
+      <s:c r="C18" s="31" t="n">
+        <s:v>271</s:v>
+      </s:c>
+      <s:c r="D18" s="31" t="n">
+        <s:v>260</s:v>
+      </s:c>
+      <s:c r="E18" s="31" t="n">
+        <s:v>244</s:v>
+      </s:c>
+      <s:c r="F18" s="31" t="n">
+        <s:v>253</s:v>
+      </s:c>
+      <s:c r="G18" s="31" t="n">
+        <s:v>290</s:v>
+      </s:c>
+      <s:c r="H18" s="31" t="n">
+        <s:v>280</s:v>
+      </s:c>
+      <s:c r="I18" s="31" t="n">
+        <s:v>294</s:v>
+      </s:c>
+      <s:c r="J18" s="31" t="n">
+        <s:v>306</s:v>
+      </s:c>
+      <s:c r="K18" s="31" t="n">
+        <s:v>338</s:v>
+      </s:c>
+      <s:c r="L18" s="31" t="n">
+        <s:v>331</s:v>
+      </s:c>
+      <s:c r="M18" s="31" t="n">
+        <s:v>333</s:v>
+      </s:c>
+      <s:c r="N18" s="31" t="n">
+        <s:v>335</s:v>
+      </s:c>
+      <s:c r="O18" s="31" t="n">
+        <s:v>375</s:v>
+      </s:c>
+      <s:c r="P18" s="31" t="n">
+        <s:v>374</s:v>
+      </s:c>
+      <s:c r="Q18" s="31" t="n">
+        <s:v>359.0948816686723</s:v>
+      </s:c>
+      <s:c r="R18" s="31" t="n">
+        <s:v>369.0251183313277</s:v>
+      </s:c>
+      <s:c r="S18" s="31" t="n">
+        <s:v>414.1237900800001</s:v>
+      </s:c>
+      <s:c r="T18" s="31" t="n">
+        <s:v>400.79641536</s:v>
+      </s:c>
+      <s:c r="U18" s="31" t="n">
+        <s:v>399.65871264</s:v>
+      </s:c>
+      <s:c r="V18" s="31" t="n">
+        <s:v>410.71068192</s:v>
+      </s:c>
+      <s:c r="X18" s="32">
+        <s:f>SUM(C18:F18)</s:f>
+        <s:v>1028.0</s:v>
+      </s:c>
+      <s:c r="Y18" s="32">
+        <s:f>SUM(G18:J18)</s:f>
+        <s:v>1170.0</s:v>
+      </s:c>
+      <s:c r="Z18" s="32">
+        <s:f>SUM(K18:N18)</s:f>
+        <s:v>1337.0</s:v>
+      </s:c>
+      <s:c r="AA18" s="32">
+        <s:f>SUM(O18:R18)</s:f>
+        <s:v>1477.12</s:v>
+      </s:c>
+      <s:c r="AB18" s="32">
+        <s:f>SUM(S18:V18)</s:f>
+        <s:v>1625.2896000000003</s:v>
+      </s:c>
     </s:row>
     <s:row r="19">
       <s:c r="A19" s="8" t="inlineStr">
@@ -13647,12 +14135,86 @@
           <s:t xml:space="preserve">    Sales &amp; marketing (cash)</s:t>
         </s:is>
       </s:c>
-      <s:c r="Q19" s="31" t="n"/>
-      <s:c r="R19" s="31" t="n"/>
-      <s:c r="S19" s="31" t="n"/>
-      <s:c r="T19" s="31" t="n"/>
-      <s:c r="U19" s="31" t="n"/>
-      <s:c r="V19" s="31" t="n"/>
+      <s:c r="C19" s="31" t="n">
+        <s:v>422</s:v>
+      </s:c>
+      <s:c r="D19" s="31" t="n">
+        <s:v>450</s:v>
+      </s:c>
+      <s:c r="E19" s="31" t="n">
+        <s:v>370</s:v>
+      </s:c>
+      <s:c r="F19" s="31" t="n">
+        <s:v>391</s:v>
+      </s:c>
+      <s:c r="G19" s="31" t="n">
+        <s:v>479</s:v>
+      </s:c>
+      <s:c r="H19" s="31" t="n">
+        <s:v>527</s:v>
+      </s:c>
+      <s:c r="I19" s="31" t="n">
+        <s:v>471</s:v>
+      </s:c>
+      <s:c r="J19" s="31" t="n">
+        <s:v>501</s:v>
+      </s:c>
+      <s:c r="K19" s="31" t="n">
+        <s:v>519</s:v>
+      </s:c>
+      <s:c r="L19" s="31" t="n">
+        <s:v>639</s:v>
+      </s:c>
+      <s:c r="M19" s="31" t="n">
+        <s:v>585</s:v>
+      </s:c>
+      <s:c r="N19" s="31" t="n">
+        <s:v>633</s:v>
+      </s:c>
+      <s:c r="O19" s="31" t="n">
+        <s:v>696</s:v>
+      </s:c>
+      <s:c r="P19" s="31" t="n">
+        <s:v>808</s:v>
+      </s:c>
+      <s:c r="Q19" s="31" t="n">
+        <s:v>778.3158128157291</s:v>
+      </s:c>
+      <s:c r="R19" s="31" t="n">
+        <s:v>758.1075295918367</s:v>
+      </s:c>
+      <s:c r="S19" s="31" t="n">
+        <s:v>829.2717874113573</s:v>
+      </s:c>
+      <s:c r="T19" s="31" t="n">
+        <s:v>935.1362709106796</s:v>
+      </s:c>
+      <s:c r="U19" s="31" t="n">
+        <s:v>819.9308035731818</s:v>
+      </s:c>
+      <s:c r="V19" s="31" t="n">
+        <s:v>875.2847818734812</s:v>
+      </s:c>
+      <s:c r="X19" s="32">
+        <s:f>SUM(C19:F19)</s:f>
+        <s:v>1633.0</s:v>
+      </s:c>
+      <s:c r="Y19" s="32">
+        <s:f>SUM(G19:J19)</s:f>
+        <s:v>1978.0</s:v>
+      </s:c>
+      <s:c r="Z19" s="32">
+        <s:f>SUM(K19:N19)</s:f>
+        <s:v>2376.0</s:v>
+      </s:c>
+      <s:c r="AA19" s="32">
+        <s:f>SUM(O19:R19)</s:f>
+        <s:v>3040.423342407566</s:v>
+      </s:c>
+      <s:c r="AB19" s="32">
+        <s:f>SUM(S19:V19)</s:f>
+        <s:v>3459.6236437687003</s:v>
+      </s:c>
     </s:row>
     <s:row r="20">
       <s:c r="A20" s="8" t="inlineStr">
@@ -13660,12 +14222,91 @@
           <s:t xml:space="preserve">    General &amp; administrative (cash, ex lodging-tax reserves)</s:t>
         </s:is>
       </s:c>
-      <s:c r="Q20" s="31" t="n"/>
-      <s:c r="R20" s="31" t="n"/>
-      <s:c r="S20" s="31" t="n"/>
-      <s:c r="T20" s="31" t="n"/>
-      <s:c r="U20" s="31" t="n"/>
-      <s:c r="V20" s="31" t="n"/>
+      <s:c r="B20" s="4" t="inlineStr">
+        <s:is>
+          <s:t>ex lodging/withholding-tax reserves (4Q23 carried $931m); reserves sit in the add-back row</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C20" s="31" t="n">
+        <s:v>191</s:v>
+      </s:c>
+      <s:c r="D20" s="31" t="n">
+        <s:v>219</s:v>
+      </s:c>
+      <s:c r="E20" s="31" t="n">
+        <s:v>202</s:v>
+      </s:c>
+      <s:c r="F20" s="31" t="n">
+        <s:v>211</s:v>
+      </s:c>
+      <s:c r="G20" s="31" t="n">
+        <s:v>223</s:v>
+      </s:c>
+      <s:c r="H20" s="31" t="n">
+        <s:v>242</s:v>
+      </s:c>
+      <s:c r="I20" s="31" t="n">
+        <s:v>210</s:v>
+      </s:c>
+      <s:c r="J20" s="31" t="n">
+        <s:v>226</s:v>
+      </s:c>
+      <s:c r="K20" s="31" t="n">
+        <s:v>235</s:v>
+      </s:c>
+      <s:c r="L20" s="31" t="n">
+        <s:v>244</s:v>
+      </s:c>
+      <s:c r="M20" s="31" t="n">
+        <s:v>257</s:v>
+      </s:c>
+      <s:c r="N20" s="31" t="n">
+        <s:v>259</s:v>
+      </s:c>
+      <s:c r="O20" s="31" t="n">
+        <s:v>226</s:v>
+      </s:c>
+      <s:c r="P20" s="31" t="n">
+        <s:v>227</s:v>
+      </s:c>
+      <s:c r="Q20" s="31" t="n">
+        <s:v>265.3890706023136</s:v>
+      </s:c>
+      <s:c r="R20" s="31" t="n">
+        <s:v>276.4109293976865</s:v>
+      </s:c>
+      <s:c r="S20" s="31" t="n">
+        <s:v>249.227244</s:v>
+      </s:c>
+      <s:c r="T20" s="31" t="n">
+        <s:v>271.5804000000001</s:v>
+      </s:c>
+      <s:c r="U20" s="31" t="n">
+        <s:v>256.539024</s:v>
+      </s:c>
+      <s:c r="V20" s="31" t="n">
+        <s:v>267.1933320000001</s:v>
+      </s:c>
+      <s:c r="X20" s="32">
+        <s:f>SUM(C20:F20)</s:f>
+        <s:v>823.0</s:v>
+      </s:c>
+      <s:c r="Y20" s="32">
+        <s:f>SUM(G20:J20)</s:f>
+        <s:v>901.0</s:v>
+      </s:c>
+      <s:c r="Z20" s="32">
+        <s:f>SUM(K20:N20)</s:f>
+        <s:v>995.0</s:v>
+      </s:c>
+      <s:c r="AA20" s="32">
+        <s:f>SUM(O20:R20)</s:f>
+        <s:v>994.8000000000002</s:v>
+      </s:c>
+      <s:c r="AB20" s="32">
+        <s:f>SUM(S20:V20)</s:f>
+        <s:v>1044.5400000000002</s:v>
+      </s:c>
     </s:row>
     <s:row r="21">
       <s:c r="A21" s="2" t="inlineStr">
@@ -13673,12 +14314,106 @@
           <s:t>Total cash costs</s:t>
         </s:is>
       </s:c>
-      <s:c r="Q21" s="31" t="n"/>
-      <s:c r="R21" s="31" t="n"/>
-      <s:c r="S21" s="31" t="n"/>
-      <s:c r="T21" s="31" t="n"/>
-      <s:c r="U21" s="31" t="n"/>
-      <s:c r="V21" s="31" t="n"/>
+      <s:c r="C21" s="32">
+        <s:f>SUM(C16:C20)</s:f>
+        <s:v>1579.0</s:v>
+      </s:c>
+      <s:c r="D21" s="32">
+        <s:f>SUM(D16:D20)</s:f>
+        <s:v>1659.0</s:v>
+      </s:c>
+      <s:c r="E21" s="32">
+        <s:f>SUM(E16:E20)</s:f>
+        <s:v>1574.0</s:v>
+      </s:c>
+      <s:c r="F21" s="32">
+        <s:f>SUM(F16:F20)</s:f>
+        <s:v>1493.0</s:v>
+      </s:c>
+      <s:c r="G21" s="32">
+        <s:f>SUM(G16:G20)</s:f>
+        <s:v>1738.0</s:v>
+      </s:c>
+      <s:c r="H21" s="32">
+        <s:f>SUM(H16:H20)</s:f>
+        <s:v>1869.0</s:v>
+      </s:c>
+      <s:c r="I21" s="32">
+        <s:f>SUM(I16:I20)</s:f>
+        <s:v>1787.0</s:v>
+      </s:c>
+      <s:c r="J21" s="32">
+        <s:f>SUM(J16:J20)</s:f>
+        <s:v>1725.0</s:v>
+      </s:c>
+      <s:c r="K21" s="32">
+        <s:f>SUM(K16:K20)</s:f>
+        <s:v>1880.0</s:v>
+      </s:c>
+      <s:c r="L21" s="32">
+        <s:f>SUM(L16:L20)</s:f>
+        <s:v>2067.0</s:v>
+      </s:c>
+      <s:c r="M21" s="32">
+        <s:f>SUM(M16:M20)</s:f>
+        <s:v>2067.0</s:v>
+      </s:c>
+      <s:c r="N21" s="32">
+        <s:f>SUM(N16:N20)</s:f>
+        <s:v>2017.0</s:v>
+      </s:c>
+      <s:c r="O21" s="32">
+        <s:f>SUM(O16:O20)</s:f>
+        <s:v>2179.0</s:v>
+      </s:c>
+      <s:c r="P21" s="32">
+        <s:f>SUM(P16:P20)</s:f>
+        <s:v>2365.0</s:v>
+      </s:c>
+      <s:c r="Q21" s="32">
+        <s:f>SUM(Q16:Q20)</s:f>
+        <s:v>2405.0269705999076</s:v>
+      </s:c>
+      <s:c r="R21" s="32">
+        <s:f>SUM(R16:R20)</s:f>
+        <s:v>2299.870129274637</s:v>
+      </s:c>
+      <s:c r="S21" s="32">
+        <s:f>SUM(S16:S20)</s:f>
+        <s:v>2517.7125008010617</s:v>
+      </s:c>
+      <s:c r="T21" s="32">
+        <s:f>SUM(T16:T20)</s:f>
+        <s:v>2675.780872847725</s:v>
+      </s:c>
+      <s:c r="U21" s="32">
+        <s:f>SUM(U16:U20)</s:f>
+        <s:v>2557.3413142838926</s:v>
+      </s:c>
+      <s:c r="V21" s="32">
+        <s:f>SUM(V16:V20)</s:f>
+        <s:v>2516.103559175239</s:v>
+      </s:c>
+      <s:c r="X21" s="32">
+        <s:f>SUM(C21:F21)</s:f>
+        <s:v>6305.0</s:v>
+      </s:c>
+      <s:c r="Y21" s="32">
+        <s:f>SUM(G21:J21)</s:f>
+        <s:v>7119.0</s:v>
+      </s:c>
+      <s:c r="Z21" s="32">
+        <s:f>SUM(K21:N21)</s:f>
+        <s:v>8031.0</s:v>
+      </s:c>
+      <s:c r="AA21" s="32">
+        <s:f>SUM(O21:R21)</s:f>
+        <s:v>9248.897099874544</s:v>
+      </s:c>
+      <s:c r="AB21" s="32">
+        <s:f>SUM(S21:V21)</s:f>
+        <s:v>10266.938247107919</s:v>
+      </s:c>
     </s:row>
     <s:row r="22">
       <s:c r="A22" s="8" t="inlineStr">
@@ -13686,12 +14421,106 @@
           <s:t xml:space="preserve">    % of revenue</s:t>
         </s:is>
       </s:c>
-      <s:c r="Q22" s="31" t="n"/>
-      <s:c r="R22" s="31" t="n"/>
-      <s:c r="S22" s="31" t="n"/>
-      <s:c r="T22" s="31" t="n"/>
-      <s:c r="U22" s="31" t="n"/>
-      <s:c r="V22" s="31" t="n"/>
+      <s:c r="C22" s="10">
+        <s:f>C21/C12</s:f>
+        <s:v>0.8685368536853685</s:v>
+      </s:c>
+      <s:c r="D22" s="10">
+        <s:f>D21/D12</s:f>
+        <s:v>0.6678743961352657</s:v>
+      </s:c>
+      <s:c r="E22" s="10">
+        <s:f>E21/E12</s:f>
+        <s:v>0.4633500147188696</s:v>
+      </s:c>
+      <s:c r="F22" s="10">
+        <s:f>F21/F12</s:f>
+        <s:v>0.6731289449954915</s:v>
+      </s:c>
+      <s:c r="G22" s="10">
+        <s:f>G21/G12</s:f>
+        <s:v>0.811391223155929</s:v>
+      </s:c>
+      <s:c r="H22" s="10">
+        <s:f>H21/H12</s:f>
+        <s:v>0.6801310043668122</s:v>
+      </s:c>
+      <s:c r="I22" s="10">
+        <s:f>I21/I12</s:f>
+        <s:v>0.47883172561629156</s:v>
+      </s:c>
+      <s:c r="J22" s="10">
+        <s:f>J21/J12</s:f>
+        <s:v>0.6955645161290323</s:v>
+      </s:c>
+      <s:c r="K22" s="10">
+        <s:f>K21/K12</s:f>
+        <s:v>0.8274647887323944</s:v>
+      </s:c>
+      <s:c r="L22" s="10">
+        <s:f>L21/L12</s:f>
+        <s:v>0.6676356589147286</s:v>
+      </s:c>
+      <s:c r="M22" s="10">
+        <s:f>M21/M12</s:f>
+        <s:v>0.5047619047619047</s:v>
+      </s:c>
+      <s:c r="N22" s="10">
+        <s:f>N21/N12</s:f>
+        <s:v>0.7260619150467963</s:v>
+      </s:c>
+      <s:c r="O22" s="10">
+        <s:f>O21/O12</s:f>
+        <s:v>0.8136669156086632</s:v>
+      </s:c>
+      <s:c r="P22" s="10">
+        <s:f>P21/P12</s:f>
+        <s:v>0.6554878048780488</s:v>
+      </s:c>
+      <s:c r="Q22" s="10">
+        <s:f>Q21/Q12</s:f>
+        <s:v>0.5126988579701665</s:v>
+      </s:c>
+      <s:c r="R22" s="10">
+        <s:f>R21/R12</s:f>
+        <s:v>0.732256219447285</s:v>
+      </s:c>
+      <s:c r="S22" s="10">
+        <s:f>S21/S12</s:f>
+        <s:v>0.8519886297030729</s:v>
+      </s:c>
+      <s:c r="T22" s="10">
+        <s:f>T21/T12</s:f>
+        <s:v>0.6816188022329719</s:v>
+      </s:c>
+      <s:c r="U22" s="10">
+        <s:f>U21/U12</s:f>
+        <s:v>0.4996986002855163</s:v>
+      </s:c>
+      <s:c r="V22" s="10">
+        <s:f>V21/V12</s:f>
+        <s:v>0.7343647211941129</s:v>
+      </s:c>
+      <s:c r="X22" s="10">
+        <s:f>X21/X12</s:f>
+        <s:v>0.6357769486739941</s:v>
+      </s:c>
+      <s:c r="Y22" s="10">
+        <s:f>Y21/Y12</s:f>
+        <s:v>0.6412358133669609</s:v>
+      </s:c>
+      <s:c r="Z22" s="10">
+        <s:f>Z21/Z12</s:f>
+        <s:v>0.6560738501756392</s:v>
+      </s:c>
+      <s:c r="AA22" s="10">
+        <s:f>AA21/AA12</s:f>
+        <s:v>0.6551270526589257</s:v>
+      </s:c>
+      <s:c r="AB22" s="10">
+        <s:f>AB21/AB12</s:f>
+        <s:v>0.6656155670167041</s:v>
+      </s:c>
     </s:row>
     <s:row r="23">
       <s:c r="A23" s="8" t="inlineStr">
@@ -13699,12 +14528,86 @@
           <s:t xml:space="preserve">    Depreciation &amp; amortisation</s:t>
         </s:is>
       </s:c>
-      <s:c r="Q23" s="31" t="n"/>
-      <s:c r="R23" s="31" t="n"/>
-      <s:c r="S23" s="31" t="n"/>
-      <s:c r="T23" s="31" t="n"/>
-      <s:c r="U23" s="31" t="n"/>
-      <s:c r="V23" s="31" t="n"/>
+      <s:c r="C23" s="31" t="n">
+        <s:v>11</s:v>
+      </s:c>
+      <s:c r="D23" s="31" t="n">
+        <s:v>9</s:v>
+      </s:c>
+      <s:c r="E23" s="31" t="n">
+        <s:v>8</s:v>
+      </s:c>
+      <s:c r="F23" s="31" t="n">
+        <s:v>16</s:v>
+      </s:c>
+      <s:c r="G23" s="31" t="n">
+        <s:v>14</s:v>
+      </s:c>
+      <s:c r="H23" s="31" t="n">
+        <s:v>14</s:v>
+      </s:c>
+      <s:c r="I23" s="31" t="n">
+        <s:v>15</s:v>
+      </s:c>
+      <s:c r="J23" s="31" t="n">
+        <s:v>22</s:v>
+      </s:c>
+      <s:c r="K23" s="31" t="n">
+        <s:v>25</s:v>
+      </s:c>
+      <s:c r="L23" s="31" t="n">
+        <s:v>21</s:v>
+      </s:c>
+      <s:c r="M23" s="31" t="n">
+        <s:v>22</s:v>
+      </s:c>
+      <s:c r="N23" s="31" t="n">
+        <s:v>23</s:v>
+      </s:c>
+      <s:c r="O23" s="31" t="n">
+        <s:v>22</s:v>
+      </s:c>
+      <s:c r="P23" s="31" t="n">
+        <s:v>17</s:v>
+      </s:c>
+      <s:c r="Q23" s="31" t="n">
+        <s:v>20.63397059990752</s:v>
+      </s:c>
+      <s:c r="R23" s="31" t="n">
+        <s:v>20.63397059990752</s:v>
+      </s:c>
+      <s:c r="S23" s="31" t="n">
+        <s:v>20.63397059990752</s:v>
+      </s:c>
+      <s:c r="T23" s="31" t="n">
+        <s:v>20.63397059990752</s:v>
+      </s:c>
+      <s:c r="U23" s="31" t="n">
+        <s:v>20.63397059990752</s:v>
+      </s:c>
+      <s:c r="V23" s="31" t="n">
+        <s:v>20.63397059990752</s:v>
+      </s:c>
+      <s:c r="X23" s="32">
+        <s:f>SUM(C23:F23)</s:f>
+        <s:v>44.0</s:v>
+      </s:c>
+      <s:c r="Y23" s="32">
+        <s:f>SUM(G23:J23)</s:f>
+        <s:v>65.0</s:v>
+      </s:c>
+      <s:c r="Z23" s="32">
+        <s:f>SUM(K23:N23)</s:f>
+        <s:v>91.0</s:v>
+      </s:c>
+      <s:c r="AA23" s="32">
+        <s:f>SUM(O23:R23)</s:f>
+        <s:v>80.26794119981504</s:v>
+      </s:c>
+      <s:c r="AB23" s="32">
+        <s:f>SUM(S23:V23)</s:f>
+        <s:v>82.53588239963008</s:v>
+      </s:c>
     </s:row>
     <s:row r="24">
       <s:c r="A24" s="2" t="inlineStr">
@@ -13712,12 +14615,97 @@
           <s:t>Adjusted EBITDA</s:t>
         </s:is>
       </s:c>
-      <s:c r="Q24" s="31" t="n"/>
-      <s:c r="R24" s="31" t="n"/>
-      <s:c r="S24" s="31" t="n"/>
-      <s:c r="T24" s="31" t="n"/>
-      <s:c r="U24" s="31" t="n"/>
-      <s:c r="V24" s="31" t="n"/>
+      <s:c r="B24" s="4" t="inlineStr">
+        <s:is>
+          <s:t>A: as reported. E: = revenue - cash costs + D&amp;A + add-backs; margin is therefore an OUTPUT</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C24" s="31" t="n">
+        <s:v>262</s:v>
+      </s:c>
+      <s:c r="D24" s="31" t="n">
+        <s:v>819</s:v>
+      </s:c>
+      <s:c r="E24" s="31" t="n">
+        <s:v>1834</s:v>
+      </s:c>
+      <s:c r="F24" s="31" t="n">
+        <s:v>738</s:v>
+      </s:c>
+      <s:c r="G24" s="31" t="n">
+        <s:v>424</s:v>
+      </s:c>
+      <s:c r="H24" s="31" t="n">
+        <s:v>894</s:v>
+      </s:c>
+      <s:c r="I24" s="31" t="n">
+        <s:v>1958</s:v>
+      </s:c>
+      <s:c r="J24" s="31" t="n">
+        <s:v>765</s:v>
+      </s:c>
+      <s:c r="K24" s="31" t="n">
+        <s:v>417</s:v>
+      </s:c>
+      <s:c r="L24" s="31" t="n">
+        <s:v>1043</s:v>
+      </s:c>
+      <s:c r="M24" s="31" t="n">
+        <s:v>2051</s:v>
+      </s:c>
+      <s:c r="N24" s="31" t="n">
+        <s:v>786</s:v>
+      </s:c>
+      <s:c r="O24" s="31" t="n">
+        <s:v>519</s:v>
+      </s:c>
+      <s:c r="P24" s="31" t="n">
+        <s:v>1261</s:v>
+      </s:c>
+      <s:c r="Q24" s="32">
+        <s:f>Q12-Q21+Q23+Q26</s:f>
+        <s:v>2306.5224042622312</s:v>
+      </s:c>
+      <s:c r="R24" s="32">
+        <s:f>R12-R21+R23+R26</s:f>
+        <s:v>861.5635616890031</s:v>
+      </s:c>
+      <s:c r="S24" s="32">
+        <s:f>S12-S21+S23+S26</s:f>
+        <s:v>458.02252751896043</s:v>
+      </s:c>
+      <s:c r="T24" s="32">
+        <s:f>T12-T21+T23+T26</s:f>
+        <s:v>1270.4796562947454</s:v>
+      </s:c>
+      <s:c r="U24" s="32">
+        <s:f>U12-U21+U23+U26</s:f>
+        <s:v>2581.060272280291</s:v>
+      </s:c>
+      <s:c r="V24" s="32">
+        <s:f>V12-V21+V23+V26</s:f>
+        <s:v>930.7619372037552</s:v>
+      </s:c>
+      <s:c r="X24" s="32">
+        <s:f>SUM(C24:F24)</s:f>
+        <s:v>3653.0</s:v>
+      </s:c>
+      <s:c r="Y24" s="32">
+        <s:f>SUM(G24:J24)</s:f>
+        <s:v>4041.0</s:v>
+      </s:c>
+      <s:c r="Z24" s="32">
+        <s:f>SUM(K24:N24)</s:f>
+        <s:v>4297.0</s:v>
+      </s:c>
+      <s:c r="AA24" s="32">
+        <s:f>SUM(O24:R24)</s:f>
+        <s:v>4948.085965951234</s:v>
+      </s:c>
+      <s:c r="AB24" s="32">
+        <s:f>SUM(S24:V24)</s:f>
+        <s:v>5240.324393297752</s:v>
+      </s:c>
     </s:row>
     <s:row r="25">
       <s:c r="A25" s="8" t="inlineStr">
@@ -13725,12 +14713,193 @@
           <s:t xml:space="preserve">    Adjusted EBITDA margin</s:t>
         </s:is>
       </s:c>
-      <s:c r="Q25" s="31" t="n"/>
-      <s:c r="R25" s="31" t="n"/>
-      <s:c r="S25" s="31" t="n"/>
-      <s:c r="T25" s="31" t="n"/>
-      <s:c r="U25" s="31" t="n"/>
-      <s:c r="V25" s="31" t="n"/>
+      <s:c r="C25" s="10">
+        <s:f>C24/C12</s:f>
+        <s:v>0.14411441144114412</s:v>
+      </s:c>
+      <s:c r="D25" s="10">
+        <s:f>D24/D12</s:f>
+        <s:v>0.32971014492753625</s:v>
+      </s:c>
+      <s:c r="E25" s="10">
+        <s:f>E24/E12</s:f>
+        <s:v>0.5398881365911098</s:v>
+      </s:c>
+      <s:c r="F25" s="10">
+        <s:f>F24/F12</s:f>
+        <s:v>0.3327321911632101</s:v>
+      </s:c>
+      <s:c r="G25" s="10">
+        <s:f>G24/G12</s:f>
+        <s:v>0.19794584500466852</s:v>
+      </s:c>
+      <s:c r="H25" s="10">
+        <s:f>H24/H12</s:f>
+        <s:v>0.32532751091703055</s:v>
+      </s:c>
+      <s:c r="I25" s="10">
+        <s:f>I24/I12</s:f>
+        <s:v>0.5246516613076099</s:v>
+      </s:c>
+      <s:c r="J25" s="10">
+        <s:f>J24/J12</s:f>
+        <s:v>0.3084677419354839</s:v>
+      </s:c>
+      <s:c r="K25" s="10">
+        <s:f>K24/K12</s:f>
+        <s:v>0.1835387323943662</s:v>
+      </s:c>
+      <s:c r="L25" s="10">
+        <s:f>L24/L12</s:f>
+        <s:v>0.33688630490956073</s:v>
+      </s:c>
+      <s:c r="M25" s="10">
+        <s:f>M24/M12</s:f>
+        <s:v>0.5008547008547009</s:v>
+      </s:c>
+      <s:c r="N25" s="10">
+        <s:f>N24/N12</s:f>
+        <s:v>0.28293736501079914</s:v>
+      </s:c>
+      <s:c r="O25" s="10">
+        <s:f>O24/O12</s:f>
+        <s:v>0.19380134428678117</s:v>
+      </s:c>
+      <s:c r="P25" s="10">
+        <s:f>P24/P12</s:f>
+        <s:v>0.3495011086474501</s:v>
+      </s:c>
+      <s:c r="Q25" s="10">
+        <s:f>Q24/Q12</s:f>
+        <s:v>0.49169985077251505</s:v>
+      </s:c>
+      <s:c r="R25" s="10">
+        <s:f>R24/R12</s:f>
+        <s:v>0.2743134355568608</s:v>
+      </s:c>
+      <s:c r="S25" s="10">
+        <s:f>S24/S12</s:f>
+        <s:v>0.15499386267091952</s:v>
+      </s:c>
+      <s:c r="T25" s="10">
+        <s:f>T24/T12</s:f>
+        <s:v>0.32363742127484146</s:v>
+      </s:c>
+      <s:c r="U25" s="10">
+        <s:f>U24/U12</s:f>
+        <s:v>0.5043332300257198</s:v>
+      </s:c>
+      <s:c r="V25" s="10">
+        <s:f>V24/V12</s:f>
+        <s:v>0.27165763031501805</s:v>
+      </s:c>
+      <s:c r="X25" s="10">
+        <s:f>X24/X12</s:f>
+        <s:v>0.3683573661389533</s:v>
+      </s:c>
+      <s:c r="Y25" s="10">
+        <s:f>Y24/Y12</s:f>
+        <s:v>0.3639884705458476</s:v>
+      </s:c>
+      <s:c r="Z25" s="10">
+        <s:f>Z24/Z12</s:f>
+        <s:v>0.3510334123029164</s:v>
+      </s:c>
+      <s:c r="AA25" s="10">
+        <s:f>AA24/AA12</s:f>
+        <s:v>0.35048773277200757</s:v>
+      </s:c>
+      <s:c r="AB25" s="10">
+        <s:f>AB24/AB12</s:f>
+        <s:v>0.3397353143113422</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="26">
+      <s:c r="B26" s="4" t="inlineStr">
+        <s:is>
+          <s:t>memo, feeds Adj. EBITDA: lodging-tax reserves and other add-backs (acquisition, IPO, restructuring)</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C26" s="31" t="n">
+        <s:v>12</s:v>
+      </s:c>
+      <s:c r="D26" s="31" t="n">
+        <s:v>-15</s:v>
+      </s:c>
+      <s:c r="E26" s="31" t="n">
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="F26" s="31" t="n">
+        <s:v>-3</s:v>
+      </s:c>
+      <s:c r="G26" s="31" t="n">
+        <s:v>6</s:v>
+      </s:c>
+      <s:c r="H26" s="31" t="n">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="I26" s="31" t="n">
+        <s:v>-2</s:v>
+      </s:c>
+      <s:c r="J26" s="31" t="n">
+        <s:v>-12</s:v>
+      </s:c>
+      <s:c r="K26" s="31" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L26" s="31" t="n">
+        <s:v>-7</s:v>
+      </s:c>
+      <s:c r="M26" s="31" t="n">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="N26" s="31" t="n">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="O26" s="31" t="n">
+        <s:v>-2</s:v>
+      </s:c>
+      <s:c r="P26" s="31" t="n">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="Q26" s="31" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="R26" s="31" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="S26" s="31" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="T26" s="31" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="U26" s="31" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="V26" s="31" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="X26" s="32">
+        <s:f>SUM(C26:F26)</s:f>
+        <s:v>-3.0</s:v>
+      </s:c>
+      <s:c r="Y26" s="32">
+        <s:f>SUM(G26:J26)</s:f>
+        <s:v>-7.0</s:v>
+      </s:c>
+      <s:c r="Z26" s="32">
+        <s:f>SUM(K26:N26)</s:f>
+        <s:v>-4.0</s:v>
+      </s:c>
+      <s:c r="AA26" s="32">
+        <s:f>SUM(O26:R26)</s:f>
+        <s:v>-1.0</s:v>
+      </s:c>
+      <s:c r="AB26" s="32">
+        <s:f>SUM(S26:V26)</s:f>
+        <s:v>0.0</s:v>
+      </s:c>
     </s:row>
     <s:row r="27">
       <s:c r="A27" s="8" t="inlineStr">
@@ -13738,12 +14907,91 @@
           <s:t xml:space="preserve">    Stock-based compensation</s:t>
         </s:is>
       </s:c>
-      <s:c r="Q27" s="31" t="n"/>
-      <s:c r="R27" s="31" t="n"/>
-      <s:c r="S27" s="31" t="n"/>
-      <s:c r="T27" s="31" t="n"/>
-      <s:c r="U27" s="31" t="n"/>
-      <s:c r="V27" s="31" t="n"/>
+      <s:c r="B27" s="4" t="inlineStr">
+        <s:is>
+          <s:t>A: income-statement footnote total. E: 40_line_build (SBC[q-4] x 1.1318, M7 parameter sheet)</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C27" s="31" t="n">
+        <s:v>240</s:v>
+      </s:c>
+      <s:c r="D27" s="31" t="n">
+        <s:v>304</s:v>
+      </s:c>
+      <s:c r="E27" s="31" t="n">
+        <s:v>286</s:v>
+      </s:c>
+      <s:c r="F27" s="31" t="n">
+        <s:v>290</s:v>
+      </s:c>
+      <s:c r="G27" s="31" t="n">
+        <s:v>295</s:v>
+      </s:c>
+      <s:c r="H27" s="31" t="n">
+        <s:v>382</s:v>
+      </s:c>
+      <s:c r="I27" s="31" t="n">
+        <s:v>362</s:v>
+      </s:c>
+      <s:c r="J27" s="31" t="n">
+        <s:v>368</s:v>
+      </s:c>
+      <s:c r="K27" s="31" t="n">
+        <s:v>358</s:v>
+      </s:c>
+      <s:c r="L27" s="31" t="n">
+        <s:v>424</s:v>
+      </s:c>
+      <s:c r="M27" s="31" t="n">
+        <s:v>399</s:v>
+      </s:c>
+      <s:c r="N27" s="31" t="n">
+        <s:v>411</s:v>
+      </s:c>
+      <s:c r="O27" s="31" t="n">
+        <s:v>410</s:v>
+      </s:c>
+      <s:c r="P27" s="31" t="n">
+        <s:v>487</s:v>
+      </s:c>
+      <s:c r="Q27" s="31" t="n">
+        <s:v>451.5791856610708</s:v>
+      </s:c>
+      <s:c r="R27" s="31" t="n">
+        <s:v>465.1605145531331</s:v>
+      </s:c>
+      <s:c r="S27" s="31" t="n">
+        <s:v>464.0287371454613</s:v>
+      </s:c>
+      <s:c r="T27" s="31" t="n">
+        <s:v>551.1755975361942</s:v>
+      </s:c>
+      <s:c r="U27" s="31" t="n">
+        <s:v>511.0871201060549</s:v>
+      </s:c>
+      <s:c r="V27" s="31" t="n">
+        <s:v>526.4581613122519</s:v>
+      </s:c>
+      <s:c r="X27" s="32">
+        <s:f>SUM(C27:F27)</s:f>
+        <s:v>1120.0</s:v>
+      </s:c>
+      <s:c r="Y27" s="32">
+        <s:f>SUM(G27:J27)</s:f>
+        <s:v>1407.0</s:v>
+      </s:c>
+      <s:c r="Z27" s="32">
+        <s:f>SUM(K27:N27)</s:f>
+        <s:v>1592.0</s:v>
+      </s:c>
+      <s:c r="AA27" s="32">
+        <s:f>SUM(O27:R27)</s:f>
+        <s:v>1813.7397002142038</s:v>
+      </s:c>
+      <s:c r="AB27" s="32">
+        <s:f>SUM(S27:V27)</s:f>
+        <s:v>2052.7496160999626</s:v>
+      </s:c>
     </s:row>
     <s:row r="28">
       <s:c r="A28" s="2" t="inlineStr">
@@ -13751,12 +14999,97 @@
           <s:t>Operating income (GAAP)</s:t>
         </s:is>
       </s:c>
-      <s:c r="Q28" s="31" t="n"/>
-      <s:c r="R28" s="31" t="n"/>
-      <s:c r="S28" s="31" t="n"/>
-      <s:c r="T28" s="31" t="n"/>
-      <s:c r="U28" s="31" t="n"/>
-      <s:c r="V28" s="31" t="n"/>
+      <s:c r="B28" s="4" t="inlineStr">
+        <s:is>
+          <s:t>A: reported GAAP. E: = Adj. EBITDA - D&amp;A - SBC (holds exactly in the line build)</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C28" s="31" t="n">
+        <s:v>-5</s:v>
+      </s:c>
+      <s:c r="D28" s="31" t="n">
+        <s:v>523</s:v>
+      </s:c>
+      <s:c r="E28" s="31" t="n">
+        <s:v>1496</s:v>
+      </s:c>
+      <s:c r="F28" s="31" t="n">
+        <s:v>-496</s:v>
+      </s:c>
+      <s:c r="G28" s="31" t="n">
+        <s:v>101</s:v>
+      </s:c>
+      <s:c r="H28" s="31" t="n">
+        <s:v>497</s:v>
+      </s:c>
+      <s:c r="I28" s="31" t="n">
+        <s:v>1525</s:v>
+      </s:c>
+      <s:c r="J28" s="31" t="n">
+        <s:v>430</s:v>
+      </s:c>
+      <s:c r="K28" s="31" t="n">
+        <s:v>38</s:v>
+      </s:c>
+      <s:c r="L28" s="31" t="n">
+        <s:v>612</s:v>
+      </s:c>
+      <s:c r="M28" s="31" t="n">
+        <s:v>1625</s:v>
+      </s:c>
+      <s:c r="N28" s="31" t="n">
+        <s:v>269</s:v>
+      </s:c>
+      <s:c r="O28" s="31" t="n">
+        <s:v>86</s:v>
+      </s:c>
+      <s:c r="P28" s="31" t="n">
+        <s:v>758</s:v>
+      </s:c>
+      <s:c r="Q28" s="32">
+        <s:f>Q24-Q23-Q27</s:f>
+        <s:v>1834.3092480012529</s:v>
+      </s:c>
+      <s:c r="R28" s="32">
+        <s:f>R24-R23-R27</s:f>
+        <s:v>375.7690765359624</s:v>
+      </s:c>
+      <s:c r="S28" s="32">
+        <s:f>S24-S23-S27</s:f>
+        <s:v>-26.640180226408404</s:v>
+      </s:c>
+      <s:c r="T28" s="32">
+        <s:f>T24-T23-T27</s:f>
+        <s:v>698.6700881586436</s:v>
+      </s:c>
+      <s:c r="U28" s="32">
+        <s:f>U24-U23-U27</s:f>
+        <s:v>2049.3391815743284</s:v>
+      </s:c>
+      <s:c r="V28" s="32">
+        <s:f>V24-V23-V27</s:f>
+        <s:v>383.6698052915957</s:v>
+      </s:c>
+      <s:c r="X28" s="32">
+        <s:f>SUM(C28:F28)</s:f>
+        <s:v>1518.0</s:v>
+      </s:c>
+      <s:c r="Y28" s="32">
+        <s:f>SUM(G28:J28)</s:f>
+        <s:v>2553.0</s:v>
+      </s:c>
+      <s:c r="Z28" s="32">
+        <s:f>SUM(K28:N28)</s:f>
+        <s:v>2544.0</s:v>
+      </s:c>
+      <s:c r="AA28" s="32">
+        <s:f>SUM(O28:R28)</s:f>
+        <s:v>3054.0783245372154</s:v>
+      </s:c>
+      <s:c r="AB28" s="32">
+        <s:f>SUM(S28:V28)</s:f>
+        <s:v>3105.0388947981596</s:v>
+      </s:c>
     </s:row>
     <s:row r="29">
       <s:c r="A29" s="8" t="inlineStr">
@@ -13764,12 +15097,86 @@
           <s:t xml:space="preserve">    Interest income</s:t>
         </s:is>
       </s:c>
-      <s:c r="Q29" s="31" t="n"/>
-      <s:c r="R29" s="31" t="n"/>
-      <s:c r="S29" s="31" t="n"/>
-      <s:c r="T29" s="31" t="n"/>
-      <s:c r="U29" s="31" t="n"/>
-      <s:c r="V29" s="31" t="n"/>
+      <s:c r="C29" s="31" t="n">
+        <s:v>146</s:v>
+      </s:c>
+      <s:c r="D29" s="31" t="n">
+        <s:v>191</s:v>
+      </s:c>
+      <s:c r="E29" s="31" t="n">
+        <s:v>192</s:v>
+      </s:c>
+      <s:c r="F29" s="31" t="n">
+        <s:v>192</s:v>
+      </s:c>
+      <s:c r="G29" s="31" t="n">
+        <s:v>202</s:v>
+      </s:c>
+      <s:c r="H29" s="31" t="n">
+        <s:v>226</s:v>
+      </s:c>
+      <s:c r="I29" s="31" t="n">
+        <s:v>207</s:v>
+      </s:c>
+      <s:c r="J29" s="31" t="n">
+        <s:v>183</s:v>
+      </s:c>
+      <s:c r="K29" s="31" t="n">
+        <s:v>173</s:v>
+      </s:c>
+      <s:c r="L29" s="31" t="n">
+        <s:v>190</s:v>
+      </s:c>
+      <s:c r="M29" s="31" t="n">
+        <s:v>180</s:v>
+      </s:c>
+      <s:c r="N29" s="31" t="n">
+        <s:v>162</s:v>
+      </s:c>
+      <s:c r="O29" s="31" t="n">
+        <s:v>155</s:v>
+      </s:c>
+      <s:c r="P29" s="31" t="n">
+        <s:v>183</s:v>
+      </s:c>
+      <s:c r="Q29" s="31" t="n">
+        <s:v>183.5489337595264</s:v>
+      </s:c>
+      <s:c r="R29" s="31" t="n">
+        <s:v>165.4954652969192</s:v>
+      </s:c>
+      <s:c r="S29" s="31" t="n">
+        <s:v>180.2622584477442</s:v>
+      </s:c>
+      <s:c r="T29" s="31" t="n">
+        <s:v>202.8476930093186</s:v>
+      </s:c>
+      <s:c r="U29" s="31" t="n">
+        <s:v>191.1450853247752</s:v>
+      </s:c>
+      <s:c r="V29" s="31" t="n">
+        <s:v>171.1550764191038</s:v>
+      </s:c>
+      <s:c r="X29" s="32">
+        <s:f>SUM(C29:F29)</s:f>
+        <s:v>721.0</s:v>
+      </s:c>
+      <s:c r="Y29" s="32">
+        <s:f>SUM(G29:J29)</s:f>
+        <s:v>818.0</s:v>
+      </s:c>
+      <s:c r="Z29" s="32">
+        <s:f>SUM(K29:N29)</s:f>
+        <s:v>705.0</s:v>
+      </s:c>
+      <s:c r="AA29" s="32">
+        <s:f>SUM(O29:R29)</s:f>
+        <s:v>687.0443990564455</s:v>
+      </s:c>
+      <s:c r="AB29" s="32">
+        <s:f>SUM(S29:V29)</s:f>
+        <s:v>745.4101132009419</s:v>
+      </s:c>
     </s:row>
     <s:row r="30">
       <s:c r="A30" s="8" t="inlineStr">
@@ -13777,12 +15184,86 @@
           <s:t xml:space="preserve">    Interest expense</s:t>
         </s:is>
       </s:c>
-      <s:c r="Q30" s="31" t="n"/>
-      <s:c r="R30" s="31" t="n"/>
-      <s:c r="S30" s="31" t="n"/>
-      <s:c r="T30" s="31" t="n"/>
-      <s:c r="U30" s="31" t="n"/>
-      <s:c r="V30" s="31" t="n"/>
+      <s:c r="C30" s="31" t="n">
+        <s:v>4</s:v>
+      </s:c>
+      <s:c r="D30" s="31" t="n">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="E30" s="31" t="n">
+        <s:v>6</s:v>
+      </s:c>
+      <s:c r="F30" s="31" t="n">
+        <s:v>71</s:v>
+      </s:c>
+      <s:c r="G30" s="31" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="H30" s="31" t="n">
+        <s:v>9</s:v>
+      </s:c>
+      <s:c r="I30" s="31" t="n">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="J30" s="31" t="n">
+        <s:v>10</s:v>
+      </s:c>
+      <s:c r="K30" s="31" t="n">
+        <s:v>5</s:v>
+      </s:c>
+      <s:c r="L30" s="31" t="n">
+        <s:v>6</s:v>
+      </s:c>
+      <s:c r="M30" s="31" t="n">
+        <s:v>6</s:v>
+      </s:c>
+      <s:c r="N30" s="31" t="n">
+        <s:v>26</s:v>
+      </s:c>
+      <s:c r="O30" s="31" t="n">
+        <s:v>21</s:v>
+      </s:c>
+      <s:c r="P30" s="31" t="n">
+        <s:v>37</s:v>
+      </s:c>
+      <s:c r="Q30" s="31" t="n">
+        <s:v>37</s:v>
+      </s:c>
+      <s:c r="R30" s="31" t="n">
+        <s:v>37</s:v>
+      </s:c>
+      <s:c r="S30" s="31" t="n">
+        <s:v>37</s:v>
+      </s:c>
+      <s:c r="T30" s="31" t="n">
+        <s:v>37</s:v>
+      </s:c>
+      <s:c r="U30" s="31" t="n">
+        <s:v>37</s:v>
+      </s:c>
+      <s:c r="V30" s="31" t="n">
+        <s:v>37</s:v>
+      </s:c>
+      <s:c r="X30" s="32">
+        <s:f>SUM(C30:F30)</s:f>
+        <s:v>83.0</s:v>
+      </s:c>
+      <s:c r="Y30" s="32">
+        <s:f>SUM(G30:J30)</s:f>
+        <s:v>21.0</s:v>
+      </s:c>
+      <s:c r="Z30" s="32">
+        <s:f>SUM(K30:N30)</s:f>
+        <s:v>43.0</s:v>
+      </s:c>
+      <s:c r="AA30" s="32">
+        <s:f>SUM(O30:R30)</s:f>
+        <s:v>132.0</s:v>
+      </s:c>
+      <s:c r="AB30" s="32">
+        <s:f>SUM(S30:V30)</s:f>
+        <s:v>148.0</s:v>
+      </s:c>
     </s:row>
     <s:row r="31">
       <s:c r="A31" s="8" t="inlineStr">
@@ -13790,12 +15271,86 @@
           <s:t xml:space="preserve">    Other income / (expense), net</s:t>
         </s:is>
       </s:c>
-      <s:c r="Q31" s="31" t="n"/>
-      <s:c r="R31" s="31" t="n"/>
-      <s:c r="S31" s="31" t="n"/>
-      <s:c r="T31" s="31" t="n"/>
-      <s:c r="U31" s="31" t="n"/>
-      <s:c r="V31" s="31" t="n"/>
+      <s:c r="C31" s="31" t="n">
+        <s:v>-7</s:v>
+      </s:c>
+      <s:c r="D31" s="31" t="n">
+        <s:v>-36</s:v>
+      </s:c>
+      <s:c r="E31" s="31" t="n">
+        <s:v>-3</s:v>
+      </s:c>
+      <s:c r="F31" s="31" t="n">
+        <s:v>-8</s:v>
+      </s:c>
+      <s:c r="G31" s="31" t="n">
+        <s:v>-10</s:v>
+      </s:c>
+      <s:c r="H31" s="31" t="n">
+        <s:v>-33</s:v>
+      </s:c>
+      <s:c r="I31" s="31" t="n">
+        <s:v>5</s:v>
+      </s:c>
+      <s:c r="J31" s="31" t="n">
+        <s:v>19</s:v>
+      </s:c>
+      <s:c r="K31" s="31" t="n">
+        <s:v>-33</s:v>
+      </s:c>
+      <s:c r="L31" s="31" t="n">
+        <s:v>-17</s:v>
+      </s:c>
+      <s:c r="M31" s="31" t="n">
+        <s:v>-7</s:v>
+      </s:c>
+      <s:c r="N31" s="31" t="n">
+        <s:v>-12</s:v>
+      </s:c>
+      <s:c r="O31" s="31" t="n">
+        <s:v>61</s:v>
+      </s:c>
+      <s:c r="P31" s="31" t="n">
+        <s:v>-7</s:v>
+      </s:c>
+      <s:c r="Q31" s="31" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="R31" s="31" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="S31" s="31" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="T31" s="31" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="U31" s="31" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="V31" s="31" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="X31" s="32">
+        <s:f>SUM(C31:F31)</s:f>
+        <s:v>-54.0</s:v>
+      </s:c>
+      <s:c r="Y31" s="32">
+        <s:f>SUM(G31:J31)</s:f>
+        <s:v>-19.0</s:v>
+      </s:c>
+      <s:c r="Z31" s="32">
+        <s:f>SUM(K31:N31)</s:f>
+        <s:v>-69.0</s:v>
+      </s:c>
+      <s:c r="AA31" s="32">
+        <s:f>SUM(O31:R31)</s:f>
+        <s:v>61.400000000000006</s:v>
+      </s:c>
+      <s:c r="AB31" s="32">
+        <s:f>SUM(S31:V31)</s:f>
+        <s:v>14.8</s:v>
+      </s:c>
     </s:row>
     <s:row r="32">
       <s:c r="A32" s="2" t="inlineStr">
@@ -13803,12 +15358,92 @@
           <s:t>Pre-tax income</s:t>
         </s:is>
       </s:c>
-      <s:c r="Q32" s="31" t="n"/>
-      <s:c r="R32" s="31" t="n"/>
-      <s:c r="S32" s="31" t="n"/>
-      <s:c r="T32" s="31" t="n"/>
-      <s:c r="U32" s="31" t="n"/>
-      <s:c r="V32" s="31" t="n"/>
+      <s:c r="C32" s="31" t="n">
+        <s:v>130</s:v>
+      </s:c>
+      <s:c r="D32" s="31" t="n">
+        <s:v>676</s:v>
+      </s:c>
+      <s:c r="E32" s="31" t="n">
+        <s:v>1679</s:v>
+      </s:c>
+      <s:c r="F32" s="31" t="n">
+        <s:v>-383</s:v>
+      </s:c>
+      <s:c r="G32" s="31" t="n">
+        <s:v>293</s:v>
+      </s:c>
+      <s:c r="H32" s="31" t="n">
+        <s:v>681</s:v>
+      </s:c>
+      <s:c r="I32" s="31" t="n">
+        <s:v>1735</s:v>
+      </s:c>
+      <s:c r="J32" s="31" t="n">
+        <s:v>622</s:v>
+      </s:c>
+      <s:c r="K32" s="31" t="n">
+        <s:v>173</s:v>
+      </s:c>
+      <s:c r="L32" s="31" t="n">
+        <s:v>779</s:v>
+      </s:c>
+      <s:c r="M32" s="31" t="n">
+        <s:v>1792</s:v>
+      </s:c>
+      <s:c r="N32" s="31" t="n">
+        <s:v>393</s:v>
+      </s:c>
+      <s:c r="O32" s="31" t="n">
+        <s:v>281</s:v>
+      </s:c>
+      <s:c r="P32" s="31" t="n">
+        <s:v>897</s:v>
+      </s:c>
+      <s:c r="Q32" s="32">
+        <s:f>Q28+Q29-Q30+Q31</s:f>
+        <s:v>1984.5581817607792</s:v>
+      </s:c>
+      <s:c r="R32" s="32">
+        <s:f>R28+R29-R30+R31</s:f>
+        <s:v>507.9645418328816</s:v>
+      </s:c>
+      <s:c r="S32" s="32">
+        <s:f>S28+S29-S30+S31</s:f>
+        <s:v>120.32207822133579</s:v>
+      </s:c>
+      <s:c r="T32" s="32">
+        <s:f>T28+T29-T30+T31</s:f>
+        <s:v>868.2177811679622</s:v>
+      </s:c>
+      <s:c r="U32" s="32">
+        <s:f>U28+U29-U30+U31</s:f>
+        <s:v>2207.1842668991035</s:v>
+      </s:c>
+      <s:c r="V32" s="32">
+        <s:f>V28+V29-V30+V31</s:f>
+        <s:v>521.5248817106996</s:v>
+      </s:c>
+      <s:c r="X32" s="32">
+        <s:f>SUM(C32:F32)</s:f>
+        <s:v>2102.0</s:v>
+      </s:c>
+      <s:c r="Y32" s="32">
+        <s:f>SUM(G32:J32)</s:f>
+        <s:v>3331.0</s:v>
+      </s:c>
+      <s:c r="Z32" s="32">
+        <s:f>SUM(K32:N32)</s:f>
+        <s:v>3137.0</s:v>
+      </s:c>
+      <s:c r="AA32" s="32">
+        <s:f>SUM(O32:R32)</s:f>
+        <s:v>3670.5227235936604</s:v>
+      </s:c>
+      <s:c r="AB32" s="32">
+        <s:f>SUM(S32:V32)</s:f>
+        <s:v>3717.249007999101</s:v>
+      </s:c>
     </s:row>
     <s:row r="33">
       <s:c r="A33" s="8" t="inlineStr">
@@ -13816,12 +15451,97 @@
           <s:t xml:space="preserve">    Income tax</s:t>
         </s:is>
       </s:c>
-      <s:c r="Q33" s="31" t="n"/>
-      <s:c r="R33" s="31" t="n"/>
-      <s:c r="S33" s="31" t="n"/>
-      <s:c r="T33" s="31" t="n"/>
-      <s:c r="U33" s="31" t="n"/>
-      <s:c r="V33" s="31" t="n"/>
+      <s:c r="B33" s="4" t="inlineStr">
+        <s:is>
+          <s:t>E: effective rate 18.0% FY26 / 17.5% FY27 (M7 parameter sheet), applied to our own pre-tax</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C33" s="31" t="n">
+        <s:v>13.4</s:v>
+      </s:c>
+      <s:c r="D33" s="31" t="n">
+        <s:v>26</s:v>
+      </s:c>
+      <s:c r="E33" s="31" t="n">
+        <s:v>-2695</s:v>
+      </s:c>
+      <s:c r="F33" s="31" t="n">
+        <s:v>-34</s:v>
+      </s:c>
+      <s:c r="G33" s="31" t="n">
+        <s:v>29</s:v>
+      </s:c>
+      <s:c r="H33" s="31" t="n">
+        <s:v>126</s:v>
+      </s:c>
+      <s:c r="I33" s="31" t="n">
+        <s:v>367</s:v>
+      </s:c>
+      <s:c r="J33" s="31" t="n">
+        <s:v>161</s:v>
+      </s:c>
+      <s:c r="K33" s="31" t="n">
+        <s:v>19</s:v>
+      </s:c>
+      <s:c r="L33" s="31" t="n">
+        <s:v>137</s:v>
+      </s:c>
+      <s:c r="M33" s="31" t="n">
+        <s:v>418</s:v>
+      </s:c>
+      <s:c r="N33" s="31" t="n">
+        <s:v>52</s:v>
+      </s:c>
+      <s:c r="O33" s="31" t="n">
+        <s:v>121</s:v>
+      </s:c>
+      <s:c r="P33" s="31" t="n">
+        <s:v>81</s:v>
+      </s:c>
+      <s:c r="Q33" s="32">
+        <s:f>Q32*0.18</s:f>
+        <s:v>357.22047271694026</s:v>
+      </s:c>
+      <s:c r="R33" s="32">
+        <s:f>R32*0.18</s:f>
+        <s:v>91.43361752991868</s:v>
+      </s:c>
+      <s:c r="S33" s="32">
+        <s:f>S32*0.175</s:f>
+        <s:v>21.05636368873376</s:v>
+      </s:c>
+      <s:c r="T33" s="32">
+        <s:f>T32*0.175</s:f>
+        <s:v>151.93811170439338</s:v>
+      </s:c>
+      <s:c r="U33" s="32">
+        <s:f>U32*0.175</s:f>
+        <s:v>386.2572467073431</s:v>
+      </s:c>
+      <s:c r="V33" s="32">
+        <s:f>V32*0.175</s:f>
+        <s:v>91.26685429937241</s:v>
+      </s:c>
+      <s:c r="X33" s="32">
+        <s:f>SUM(C33:F33)</s:f>
+        <s:v>-2689.6</s:v>
+      </s:c>
+      <s:c r="Y33" s="32">
+        <s:f>SUM(G33:J33)</s:f>
+        <s:v>683.0</s:v>
+      </s:c>
+      <s:c r="Z33" s="32">
+        <s:f>SUM(K33:N33)</s:f>
+        <s:v>626.0</s:v>
+      </s:c>
+      <s:c r="AA33" s="32">
+        <s:f>SUM(O33:R33)</s:f>
+        <s:v>650.654090246859</s:v>
+      </s:c>
+      <s:c r="AB33" s="32">
+        <s:f>SUM(S33:V33)</s:f>
+        <s:v>650.5185763998427</s:v>
+      </s:c>
     </s:row>
     <s:row r="34">
       <s:c r="A34" s="2" t="inlineStr">
@@ -13829,12 +15549,92 @@
           <s:t>Net income</s:t>
         </s:is>
       </s:c>
-      <s:c r="Q34" s="31" t="n"/>
-      <s:c r="R34" s="31" t="n"/>
-      <s:c r="S34" s="31" t="n"/>
-      <s:c r="T34" s="31" t="n"/>
-      <s:c r="U34" s="31" t="n"/>
-      <s:c r="V34" s="31" t="n"/>
+      <s:c r="C34" s="31" t="n">
+        <s:v>117</s:v>
+      </s:c>
+      <s:c r="D34" s="31" t="n">
+        <s:v>650</s:v>
+      </s:c>
+      <s:c r="E34" s="31" t="n">
+        <s:v>4374</s:v>
+      </s:c>
+      <s:c r="F34" s="31" t="n">
+        <s:v>-349</s:v>
+      </s:c>
+      <s:c r="G34" s="31" t="n">
+        <s:v>264</s:v>
+      </s:c>
+      <s:c r="H34" s="31" t="n">
+        <s:v>555</s:v>
+      </s:c>
+      <s:c r="I34" s="31" t="n">
+        <s:v>1368</s:v>
+      </s:c>
+      <s:c r="J34" s="31" t="n">
+        <s:v>461</s:v>
+      </s:c>
+      <s:c r="K34" s="31" t="n">
+        <s:v>154</s:v>
+      </s:c>
+      <s:c r="L34" s="31" t="n">
+        <s:v>642</s:v>
+      </s:c>
+      <s:c r="M34" s="31" t="n">
+        <s:v>1374</s:v>
+      </s:c>
+      <s:c r="N34" s="31" t="n">
+        <s:v>341</s:v>
+      </s:c>
+      <s:c r="O34" s="31" t="n">
+        <s:v>160</s:v>
+      </s:c>
+      <s:c r="P34" s="31" t="n">
+        <s:v>816</s:v>
+      </s:c>
+      <s:c r="Q34" s="32">
+        <s:f>Q32-Q33</s:f>
+        <s:v>1627.337709043839</s:v>
+      </s:c>
+      <s:c r="R34" s="32">
+        <s:f>R32-R33</s:f>
+        <s:v>416.53092430296294</s:v>
+      </s:c>
+      <s:c r="S34" s="32">
+        <s:f>S32-S33</s:f>
+        <s:v>99.26571453260203</s:v>
+      </s:c>
+      <s:c r="T34" s="32">
+        <s:f>T32-T33</s:f>
+        <s:v>716.2796694635689</s:v>
+      </s:c>
+      <s:c r="U34" s="32">
+        <s:f>U32-U33</s:f>
+        <s:v>1820.9270201917604</s:v>
+      </s:c>
+      <s:c r="V34" s="32">
+        <s:f>V32-V33</s:f>
+        <s:v>430.25802741132713</s:v>
+      </s:c>
+      <s:c r="X34" s="32">
+        <s:f>SUM(C34:F34)</s:f>
+        <s:v>4792.0</s:v>
+      </s:c>
+      <s:c r="Y34" s="32">
+        <s:f>SUM(G34:J34)</s:f>
+        <s:v>2648.0</s:v>
+      </s:c>
+      <s:c r="Z34" s="32">
+        <s:f>SUM(K34:N34)</s:f>
+        <s:v>2511.0</s:v>
+      </s:c>
+      <s:c r="AA34" s="32">
+        <s:f>SUM(O34:R34)</s:f>
+        <s:v>3019.8686333468017</s:v>
+      </s:c>
+      <s:c r="AB34" s="32">
+        <s:f>SUM(S34:V34)</s:f>
+        <s:v>3066.7304315992583</s:v>
+      </s:c>
     </s:row>
     <s:row r="35">
       <s:c r="A35" s="8" t="inlineStr">
@@ -13842,12 +15642,86 @@
           <s:t xml:space="preserve">    Diluted shares (m)</s:t>
         </s:is>
       </s:c>
-      <s:c r="Q35" s="31" t="n"/>
-      <s:c r="R35" s="31" t="n"/>
-      <s:c r="S35" s="31" t="n"/>
-      <s:c r="T35" s="31" t="n"/>
-      <s:c r="U35" s="31" t="n"/>
-      <s:c r="V35" s="31" t="n"/>
+      <s:c r="C35" s="9" t="n">
+        <s:v>670</s:v>
+      </s:c>
+      <s:c r="D35" s="9" t="n">
+        <s:v>665</s:v>
+      </s:c>
+      <s:c r="E35" s="9" t="n">
+        <s:v>660</s:v>
+      </s:c>
+      <s:c r="F35" s="9" t="n">
+        <s:v>640</s:v>
+      </s:c>
+      <s:c r="G35" s="9" t="n">
+        <s:v>654</s:v>
+      </s:c>
+      <s:c r="H35" s="9" t="n">
+        <s:v>649</s:v>
+      </s:c>
+      <s:c r="I35" s="9" t="n">
+        <s:v>642</s:v>
+      </s:c>
+      <s:c r="J35" s="9" t="n">
+        <s:v>636</s:v>
+      </s:c>
+      <s:c r="K35" s="9" t="n">
+        <s:v>632</s:v>
+      </s:c>
+      <s:c r="L35" s="9" t="n">
+        <s:v>626</s:v>
+      </s:c>
+      <s:c r="M35" s="9" t="n">
+        <s:v>621</s:v>
+      </s:c>
+      <s:c r="N35" s="9" t="n">
+        <s:v>614</s:v>
+      </s:c>
+      <s:c r="O35" s="9" t="n">
+        <s:v>608</s:v>
+      </s:c>
+      <s:c r="P35" s="9" t="n">
+        <s:v>597</s:v>
+      </s:c>
+      <s:c r="Q35" s="9" t="n">
+        <s:v>591.6758133819055</s:v>
+      </s:c>
+      <s:c r="R35" s="9" t="n">
+        <s:v>586.3516267638111</s:v>
+      </s:c>
+      <s:c r="S35" s="9" t="n">
+        <s:v>581.0274401457166</s:v>
+      </s:c>
+      <s:c r="T35" s="9" t="n">
+        <s:v>575.7032535276221</s:v>
+      </s:c>
+      <s:c r="U35" s="9" t="n">
+        <s:v>570.3790669095276</s:v>
+      </s:c>
+      <s:c r="V35" s="9" t="n">
+        <s:v>565.0548802914332</s:v>
+      </s:c>
+      <s:c r="X35" s="22">
+        <s:f>AVERAGE(C35:F35)</s:f>
+        <s:v>658.75</s:v>
+      </s:c>
+      <s:c r="Y35" s="22">
+        <s:f>AVERAGE(G35:J35)</s:f>
+        <s:v>645.25</s:v>
+      </s:c>
+      <s:c r="Z35" s="22">
+        <s:f>AVERAGE(K35:N35)</s:f>
+        <s:v>623.25</s:v>
+      </s:c>
+      <s:c r="AA35" s="22">
+        <s:f>AVERAGE(O35:R35)</s:f>
+        <s:v>595.7568600364291</s:v>
+      </s:c>
+      <s:c r="AB35" s="22">
+        <s:f>AVERAGE(S35:V35)</s:f>
+        <s:v>573.0411602185749</s:v>
+      </s:c>
     </s:row>
     <s:row r="36">
       <s:c r="A36" s="2" t="inlineStr">
@@ -13855,12 +15729,365 @@
           <s:t>Diluted EPS ($)</s:t>
         </s:is>
       </s:c>
-      <s:c r="Q36" s="31" t="n"/>
-      <s:c r="R36" s="31" t="n"/>
-      <s:c r="S36" s="31" t="n"/>
-      <s:c r="T36" s="31" t="n"/>
-      <s:c r="U36" s="31" t="n"/>
-      <s:c r="V36" s="31" t="n"/>
+      <s:c r="B36" s="4" t="inlineStr">
+        <s:is>
+          <s:t>E: = net income / diluted shares; shares -5.324m per quarter (M7)</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C36" s="11" t="n">
+        <s:v>0.18</s:v>
+      </s:c>
+      <s:c r="D36" s="11" t="n">
+        <s:v>0.98</s:v>
+      </s:c>
+      <s:c r="E36" s="11" t="n">
+        <s:v>6.63</s:v>
+      </s:c>
+      <s:c r="F36" s="11" t="n">
+        <s:v>-0.55</s:v>
+      </s:c>
+      <s:c r="G36" s="11" t="n">
+        <s:v>0.41</s:v>
+      </s:c>
+      <s:c r="H36" s="11" t="n">
+        <s:v>0.86</s:v>
+      </s:c>
+      <s:c r="I36" s="11" t="n">
+        <s:v>2.13</s:v>
+      </s:c>
+      <s:c r="J36" s="11" t="n">
+        <s:v>0.73</s:v>
+      </s:c>
+      <s:c r="K36" s="11" t="n">
+        <s:v>0.24</s:v>
+      </s:c>
+      <s:c r="L36" s="11" t="n">
+        <s:v>1.03</s:v>
+      </s:c>
+      <s:c r="M36" s="11" t="n">
+        <s:v>2.21</s:v>
+      </s:c>
+      <s:c r="N36" s="11" t="n">
+        <s:v>0.5600000000000001</s:v>
+      </s:c>
+      <s:c r="O36" s="11" t="n">
+        <s:v>0.26</s:v>
+      </s:c>
+      <s:c r="P36" s="11" t="n">
+        <s:v>1.37</s:v>
+      </s:c>
+      <s:c r="Q36" s="15">
+        <s:f>Q34/Q35</s:f>
+        <s:v>2.7503874118874125</s:v>
+      </s:c>
+      <s:c r="R36" s="15">
+        <s:f>R34/R35</s:f>
+        <s:v>0.7103773662262666</s:v>
+      </s:c>
+      <s:c r="S36" s="15">
+        <s:f>S34/S35</s:f>
+        <s:v>0.17084514030474543</s:v>
+      </s:c>
+      <s:c r="T36" s="15">
+        <s:f>T34/T35</s:f>
+        <s:v>1.244182076572548</s:v>
+      </s:c>
+      <s:c r="U36" s="15">
+        <s:f>U34/U35</s:f>
+        <s:v>3.192485709649285</s:v>
+      </s:c>
+      <s:c r="V36" s="15">
+        <s:f>V34/V35</s:f>
+        <s:v>0.7614446709838466</s:v>
+      </s:c>
+      <s:c r="X36" s="15">
+        <s:f>X34/X35</s:f>
+        <s:v>7.27438330170778</s:v>
+      </s:c>
+      <s:c r="Y36" s="15">
+        <s:f>Y34/Y35</s:f>
+        <s:v>4.103835722588144</s:v>
+      </s:c>
+      <s:c r="Z36" s="15">
+        <s:f>Z34/Z35</s:f>
+        <s:v>4.028880866425993</s:v>
+      </s:c>
+      <s:c r="AA36" s="15">
+        <s:f>AA34/AA35</s:f>
+        <s:v>5.068961577986939</s:v>
+      </s:c>
+      <s:c r="AB36" s="15">
+        <s:f>AB34/AB35</s:f>
+        <s:v>5.351675663977639</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="38">
+      <s:c r="A38" s="5" t="inlineStr">
+        <s:is>
+          <s:t>Cross-checks against the Street, and the open choices this line does not settle (memo rows - none of these feed the statement above)</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B38" s="5" t="n"/>
+      <s:c r="C38" s="5" t="n"/>
+      <s:c r="D38" s="5" t="n"/>
+      <s:c r="E38" s="5" t="n"/>
+      <s:c r="F38" s="5" t="n"/>
+      <s:c r="G38" s="5" t="n"/>
+      <s:c r="H38" s="5" t="n"/>
+      <s:c r="I38" s="5" t="n"/>
+      <s:c r="J38" s="5" t="n"/>
+      <s:c r="K38" s="5" t="n"/>
+      <s:c r="L38" s="5" t="n"/>
+      <s:c r="M38" s="5" t="n"/>
+      <s:c r="N38" s="5" t="n"/>
+      <s:c r="O38" s="5" t="n"/>
+      <s:c r="P38" s="5" t="n"/>
+      <s:c r="Q38" s="5" t="n"/>
+      <s:c r="R38" s="5" t="n"/>
+      <s:c r="S38" s="5" t="n"/>
+      <s:c r="T38" s="5" t="n"/>
+      <s:c r="U38" s="5" t="n"/>
+      <s:c r="V38" s="5" t="n"/>
+      <s:c r="W38" s="5" t="n"/>
+      <s:c r="X38" s="5" t="n"/>
+      <s:c r="Y38" s="5" t="n"/>
+      <s:c r="Z38" s="5" t="n"/>
+      <s:c r="AA38" s="5" t="n"/>
+      <s:c r="AB38" s="5" t="n"/>
+    </s:row>
+    <s:row r="39">
+      <s:c r="A39" s="8" t="inlineStr">
+        <s:is>
+          <s:t>Street revenue ($m)</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B39" s="4" t="inlineStr">
+        <s:is>
+          <s:t>LSEG 06_consensus_quarterly_2027.csv, 13 Sep 2026 pull</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="Q39" s="31" t="n">
+        <s:v>4744.32</s:v>
+      </s:c>
+      <s:c r="R39" s="31" t="n">
+        <s:v>3161.82</s:v>
+      </s:c>
+      <s:c r="S39" s="31" t="n">
+        <s:v>3010.32</s:v>
+      </s:c>
+      <s:c r="T39" s="31" t="n">
+        <s:v>4036.94</s:v>
+      </s:c>
+      <s:c r="U39" s="31" t="n">
+        <s:v>5269.97</s:v>
+      </s:c>
+      <s:c r="V39" s="31" t="n">
+        <s:v>3528.92</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="40">
+      <s:c r="A40" s="8" t="inlineStr">
+        <s:is>
+          <s:t xml:space="preserve">    ours vs Street</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B40" s="4" t="inlineStr">
+        <s:is>
+          <s:t>negative = our nights/ADR lines sit below consensus</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="Q40" s="33">
+        <s:f>Q12/Q39-1</s:f>
+        <s:v>-0.011256533230846189</s:v>
+      </s:c>
+      <s:c r="R40" s="33">
+        <s:f>R12/R39-1</s:f>
+        <s:v>-0.006648158224145551</s:v>
+      </s:c>
+      <s:c r="S40" s="33">
+        <s:f>S12/S39-1</s:f>
+        <s:v>-0.018343213439064865</s:v>
+      </s:c>
+      <s:c r="T40" s="33">
+        <s:f>T12/T39-1</s:f>
+        <s:v>-0.027573717087060357</s:v>
+      </s:c>
+      <s:c r="U40" s="33">
+        <s:f>U12/U39-1</s:f>
+        <s:v>-0.028881072195045543</s:v>
+      </s:c>
+      <s:c r="V40" s="33">
+        <s:f>V12/V39-1</s:f>
+        <s:v>-0.02909912217361499</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="41">
+      <s:c r="A41" s="8" t="inlineStr">
+        <s:is>
+          <s:t>Street adj. EBITDA ($m)</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B41" s="4" t="inlineStr">
+        <s:is>
+          <s:t>LSEG; n 36-37 for 3Q26/4Q26, n 17-19 for 2027</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="Q41" s="31" t="n">
+        <s:v>2361.52</s:v>
+      </s:c>
+      <s:c r="R41" s="31" t="n">
+        <s:v>913.6799999999999</s:v>
+      </s:c>
+      <s:c r="S41" s="31" t="n">
+        <s:v>610.73</s:v>
+      </s:c>
+      <s:c r="T41" s="31" t="n">
+        <s:v>1451.71</s:v>
+      </s:c>
+      <s:c r="U41" s="31" t="n">
+        <s:v>2695.55</s:v>
+      </s:c>
+      <s:c r="V41" s="31" t="n">
+        <s:v>1068.4</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="42">
+      <s:c r="A42" s="8" t="inlineStr">
+        <s:is>
+          <s:t xml:space="preserve">    ours vs Street</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B42" s="4" t="inlineStr">
+        <s:is>
+          <s:t>wider than the revenue gap because cost dollars are carried flat</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="Q42" s="33">
+        <s:f>Q24/Q41-1</s:f>
+        <s:v>-0.023289066252993318</s:v>
+      </s:c>
+      <s:c r="R42" s="33">
+        <s:f>R24/R41-1</s:f>
+        <s:v>-0.05704014349772002</s:v>
+      </s:c>
+      <s:c r="S42" s="33">
+        <s:f>S24/S41-1</s:f>
+        <s:v>-0.2500408895600995</s:v>
+      </s:c>
+      <s:c r="T42" s="33">
+        <s:f>T24/T41-1</s:f>
+        <s:v>-0.12483921975136536</s:v>
+      </s:c>
+      <s:c r="U42" s="33">
+        <s:f>U24/U41-1</s:f>
+        <s:v>-0.04247360565365477</s:v>
+      </s:c>
+      <s:c r="V42" s="33">
+        <s:f>V24/V41-1</s:f>
+        <s:v>-0.12882634106724533</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="43">
+      <s:c r="A43" s="8" t="inlineStr">
+        <s:is>
+          <s:t>memo: adj. EBITDA if costs flexed to hold the line build's own margin</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B43" s="4" t="inlineStr">
+        <s:is>
+          <s:t>DEC-0022 carries dollars flat; C4 asks whether management's margin sentence is a budget (costs flex) or a floor</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="Q43" s="32">
+        <s:f>Q12*0.5036687385012039</s:f>
+        <s:v>2362.6674440806228</s:v>
+      </s:c>
+      <s:c r="R43" s="32">
+        <s:f>R12*0.2828323322844086</s:f>
+        <s:v>888.3197101486928</s:v>
+      </s:c>
+      <s:c r="S43" s="32">
+        <s:f>S12*0.18212486768865177</s:f>
+        <s:v>538.1973891438707</s:v>
+      </s:c>
+      <s:c r="T43" s="32">
+        <s:f>T12*0.34098793219639467</s:f>
+        <s:v>1338.5912827726775</s:v>
+      </s:c>
+      <s:c r="U43" s="32">
+        <s:f>U12*0.5196296453789346</s:f>
+        <s:v>2659.3437714153124</s:v>
+      </s:c>
+      <s:c r="V43" s="32">
+        <s:f>V12*0.2799655381693949</s:f>
+        <s:v>959.226753007689</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="44">
+      <s:c r="A44" s="8" t="inlineStr">
+        <s:is>
+          <s:t xml:space="preserve">    difference vs the statement above</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B44" s="4" t="inlineStr">
+        <s:is>
+          <s:t>the cost of the flat-dollar assumption, in EBITDA $m</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="Q44" s="32">
+        <s:f>Q43-Q24</s:f>
+        <s:v>56.145039818391524</s:v>
+      </s:c>
+      <s:c r="R44" s="32">
+        <s:f>R43-R24</s:f>
+        <s:v>26.75614845968971</s:v>
+      </s:c>
+      <s:c r="S44" s="32">
+        <s:f>S43-S24</s:f>
+        <s:v>80.1748616249103</s:v>
+      </s:c>
+      <s:c r="T44" s="32">
+        <s:f>T43-T24</s:f>
+        <s:v>68.11162647793208</s:v>
+      </s:c>
+      <s:c r="U44" s="32">
+        <s:f>U43-U24</s:f>
+        <s:v>78.28349913502143</s:v>
+      </s:c>
+      <s:c r="V44" s="32">
+        <s:f>V43-V24</s:f>
+        <s:v>28.46481580393379</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="45">
+      <s:c r="A45" s="8" t="inlineStr">
+        <s:is>
+          <s:t>memo: DEC-0023 hosting step, B08 alternative ($85.0m/q vs the $100.21m/$111.71m plugged)</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B45" s="4" t="inlineStr">
+        <s:is>
+          <s:t>NOT CHOSEN - both sides on record; positive = EBITDA if the lower B08 hosting number is right</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="Q45" s="31" t="n">
+        <s:v>15.20793246038539</s:v>
+      </s:c>
+      <s:c r="R45" s="31" t="n">
+        <s:v>15.20793246038539</s:v>
+      </s:c>
+      <s:c r="S45" s="31" t="n">
+        <s:v>26.70793246038539</s:v>
+      </s:c>
+      <s:c r="T45" s="31" t="n">
+        <s:v>26.70793246038539</s:v>
+      </s:c>
+      <s:c r="U45" s="31" t="n">
+        <s:v>26.70793246038539</s:v>
+      </s:c>
+      <s:c r="V45" s="31" t="n">
+        <s:v>26.70793246038539</s:v>
+      </s:c>
     </s:row>
   </s:sheetData>
   <s:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/model/ABNB_official_model_complete.xlsx
+++ b/model/ABNB_official_model_complete.xlsx
@@ -15702,17 +15702,14 @@
       <s:c r="V35" s="9" t="n">
         <s:v>565.0548802914332</s:v>
       </s:c>
-      <s:c r="X35" s="22">
-        <s:f>AVERAGE(C35:F35)</s:f>
-        <s:v>658.75</s:v>
-      </s:c>
-      <s:c r="Y35" s="22">
-        <s:f>AVERAGE(G35:J35)</s:f>
-        <s:v>645.25</s:v>
-      </s:c>
-      <s:c r="Z35" s="22">
-        <s:f>AVERAGE(K35:N35)</s:f>
-        <s:v>623.25</s:v>
+      <s:c r="X35" s="9" t="n">
+        <s:v>662</s:v>
+      </s:c>
+      <s:c r="Y35" s="9" t="n">
+        <s:v>645</s:v>
+      </s:c>
+      <s:c r="Z35" s="9" t="n">
+        <s:v>623</s:v>
       </s:c>
       <s:c r="AA35" s="22">
         <s:f>AVERAGE(O35:R35)</s:f>
@@ -15800,17 +15797,14 @@
         <s:f>V34/V35</s:f>
         <s:v>0.7614446709838466</s:v>
       </s:c>
-      <s:c r="X36" s="15">
-        <s:f>X34/X35</s:f>
-        <s:v>7.27438330170778</s:v>
-      </s:c>
-      <s:c r="Y36" s="15">
-        <s:f>Y34/Y35</s:f>
-        <s:v>4.103835722588144</s:v>
-      </s:c>
-      <s:c r="Z36" s="15">
-        <s:f>Z34/Z35</s:f>
-        <s:v>4.028880866425993</s:v>
+      <s:c r="X36" s="11" t="n">
+        <s:v>7.24</s:v>
+      </s:c>
+      <s:c r="Y36" s="11" t="n">
+        <s:v>4.11</s:v>
+      </s:c>
+      <s:c r="Z36" s="11" t="n">
+        <s:v>4.03</s:v>
       </s:c>
       <s:c r="AA36" s="15">
         <s:f>AA34/AA35</s:f>
